--- a/Actas y formatos/ActaVisita.xlsx
+++ b/Actas y formatos/ActaVisita.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10928"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leonardo.aguas\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geotrends/Desktop/CRMALCALDIA/CRMALCALDIA/Actas y formatos/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A448F10E-FB04-B441-A638-5897E9CC046C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11835"/>
+    <workbookView xWindow="39640" yWindow="600" windowWidth="28800" windowHeight="11840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="carta 2024" sheetId="1" r:id="rId1"/>
@@ -194,7 +195,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -752,141 +753,140 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -904,131 +904,131 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1064,7 +1064,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Imagen 1"/>
+        <xdr:cNvPr id="2" name="Imagen 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
@@ -1119,7 +1125,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Imagen 2"/>
+        <xdr:cNvPr id="3" name="Imagen 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
@@ -1424,494 +1436,494 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X140"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:X85"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="4" width="3.7109375" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="4.5703125" customWidth="1" collapsed="1"/>
-    <col min="6" max="16" width="3.7109375" customWidth="1" collapsed="1"/>
-    <col min="17" max="17" width="3.5703125" customWidth="1" collapsed="1"/>
-    <col min="18" max="24" width="3.7109375" customWidth="1" collapsed="1"/>
+    <col min="1" max="4" width="3.6640625" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="4.5" customWidth="1" collapsed="1"/>
+    <col min="6" max="16" width="3.6640625" customWidth="1" collapsed="1"/>
+    <col min="17" max="17" width="3.5" customWidth="1" collapsed="1"/>
+    <col min="18" max="24" width="3.6640625" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="20.100000000000001" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="56"/>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56" t="s">
+    <row r="1" spans="1:24" ht="20" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="55"/>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
-      <c r="P1" s="56"/>
-      <c r="Q1" s="56"/>
-      <c r="R1" s="56"/>
-      <c r="S1" s="56"/>
-      <c r="T1" s="59" t="s">
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="55"/>
+      <c r="L1" s="55"/>
+      <c r="M1" s="55"/>
+      <c r="N1" s="55"/>
+      <c r="O1" s="55"/>
+      <c r="P1" s="55"/>
+      <c r="Q1" s="55"/>
+      <c r="R1" s="55"/>
+      <c r="S1" s="55"/>
+      <c r="T1" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="U1" s="59"/>
-      <c r="V1" s="59"/>
-      <c r="W1" s="59"/>
-      <c r="X1" s="59"/>
-    </row>
-    <row r="2" spans="1:24" ht="20.100000000000001" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="57"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="57"/>
-      <c r="L2" s="57"/>
-      <c r="M2" s="57"/>
-      <c r="N2" s="57"/>
-      <c r="O2" s="57"/>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="57"/>
-      <c r="S2" s="57"/>
-      <c r="T2" s="59" t="s">
+      <c r="U1" s="58"/>
+      <c r="V1" s="58"/>
+      <c r="W1" s="58"/>
+      <c r="X1" s="58"/>
+    </row>
+    <row r="2" spans="1:24" ht="20" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="56"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="56"/>
+      <c r="N2" s="56"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="56"/>
+      <c r="Q2" s="56"/>
+      <c r="R2" s="56"/>
+      <c r="S2" s="56"/>
+      <c r="T2" s="58" t="s">
         <v>52</v>
       </c>
-      <c r="U2" s="59"/>
-      <c r="V2" s="59"/>
-      <c r="W2" s="59"/>
-      <c r="X2" s="59"/>
-    </row>
-    <row r="3" spans="1:24" ht="20.100000000000001" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="58"/>
-      <c r="B3" s="58"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="58"/>
-      <c r="L3" s="58"/>
-      <c r="M3" s="58"/>
-      <c r="N3" s="58"/>
-      <c r="O3" s="58"/>
-      <c r="P3" s="58"/>
-      <c r="Q3" s="58"/>
-      <c r="R3" s="58"/>
-      <c r="S3" s="58"/>
-      <c r="T3" s="60" t="s">
+      <c r="U2" s="58"/>
+      <c r="V2" s="58"/>
+      <c r="W2" s="58"/>
+      <c r="X2" s="58"/>
+    </row>
+    <row r="3" spans="1:24" ht="20" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="57"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="57"/>
+      <c r="L3" s="57"/>
+      <c r="M3" s="57"/>
+      <c r="N3" s="57"/>
+      <c r="O3" s="57"/>
+      <c r="P3" s="57"/>
+      <c r="Q3" s="57"/>
+      <c r="R3" s="57"/>
+      <c r="S3" s="57"/>
+      <c r="T3" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="U3" s="60"/>
-      <c r="V3" s="60"/>
-      <c r="W3" s="60"/>
-      <c r="X3" s="60"/>
-    </row>
-    <row r="4" spans="1:24" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="68" t="s">
+      <c r="U3" s="59"/>
+      <c r="V3" s="59"/>
+      <c r="W3" s="59"/>
+      <c r="X3" s="59"/>
+    </row>
+    <row r="4" spans="1:24" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="69"/>
-      <c r="C4" s="69"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="69"/>
-      <c r="H4" s="69"/>
-      <c r="I4" s="69"/>
-      <c r="J4" s="69"/>
-      <c r="K4" s="69"/>
-      <c r="L4" s="69"/>
-      <c r="M4" s="69"/>
-      <c r="N4" s="69"/>
-      <c r="O4" s="69"/>
-      <c r="P4" s="69"/>
-      <c r="Q4" s="69"/>
-      <c r="R4" s="69"/>
-      <c r="S4" s="69"/>
-      <c r="T4" s="69"/>
-      <c r="U4" s="69"/>
-      <c r="V4" s="69"/>
-      <c r="W4" s="69"/>
-      <c r="X4" s="98"/>
-    </row>
-    <row r="5" spans="1:24" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="100" t="s">
+      <c r="B4" s="65"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="65"/>
+      <c r="L4" s="65"/>
+      <c r="M4" s="65"/>
+      <c r="N4" s="65"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
+      <c r="U4" s="65"/>
+      <c r="V4" s="65"/>
+      <c r="W4" s="65"/>
+      <c r="X4" s="66"/>
+    </row>
+    <row r="5" spans="1:24" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="67" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="101"/>
-      <c r="C5" s="101"/>
-      <c r="D5" s="101"/>
-      <c r="E5" s="102"/>
-      <c r="F5" s="96"/>
-      <c r="G5" s="96"/>
-      <c r="H5" s="96"/>
-      <c r="I5" s="96"/>
-      <c r="J5" s="96"/>
-      <c r="K5" s="96"/>
-      <c r="L5" s="96"/>
-      <c r="M5" s="96"/>
-      <c r="N5" s="97"/>
-      <c r="O5" s="95" t="s">
+      <c r="B5" s="68"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="61"/>
+      <c r="L5" s="61"/>
+      <c r="M5" s="61"/>
+      <c r="N5" s="62"/>
+      <c r="O5" s="60" t="s">
         <v>5</v>
       </c>
-      <c r="P5" s="96"/>
-      <c r="Q5" s="97"/>
-      <c r="R5" s="95"/>
-      <c r="S5" s="96"/>
-      <c r="T5" s="96"/>
-      <c r="U5" s="96"/>
-      <c r="V5" s="96"/>
-      <c r="W5" s="96"/>
-      <c r="X5" s="97"/>
-    </row>
-    <row r="6" spans="1:24" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="100" t="s">
+      <c r="P5" s="61"/>
+      <c r="Q5" s="62"/>
+      <c r="R5" s="60"/>
+      <c r="S5" s="61"/>
+      <c r="T5" s="61"/>
+      <c r="U5" s="61"/>
+      <c r="V5" s="61"/>
+      <c r="W5" s="61"/>
+      <c r="X5" s="62"/>
+    </row>
+    <row r="6" spans="1:24" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="67" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="101"/>
-      <c r="C6" s="101"/>
-      <c r="D6" s="102"/>
-      <c r="E6" s="95"/>
-      <c r="F6" s="96"/>
-      <c r="G6" s="96"/>
-      <c r="H6" s="96"/>
-      <c r="I6" s="96"/>
-      <c r="J6" s="96"/>
-      <c r="K6" s="96"/>
-      <c r="L6" s="96"/>
-      <c r="M6" s="96"/>
-      <c r="N6" s="96"/>
-      <c r="O6" s="96"/>
-      <c r="P6" s="96"/>
-      <c r="Q6" s="97"/>
-      <c r="R6" s="95" t="s">
+      <c r="B6" s="68"/>
+      <c r="C6" s="68"/>
+      <c r="D6" s="69"/>
+      <c r="E6" s="60"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="61"/>
+      <c r="H6" s="61"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="61"/>
+      <c r="L6" s="61"/>
+      <c r="M6" s="61"/>
+      <c r="N6" s="61"/>
+      <c r="O6" s="61"/>
+      <c r="P6" s="61"/>
+      <c r="Q6" s="62"/>
+      <c r="R6" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="S6" s="97"/>
-      <c r="T6" s="96"/>
-      <c r="U6" s="96"/>
-      <c r="V6" s="96"/>
-      <c r="W6" s="96"/>
-      <c r="X6" s="97"/>
-    </row>
-    <row r="7" spans="1:24" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S6" s="62"/>
+      <c r="T6" s="61"/>
+      <c r="U6" s="61"/>
+      <c r="V6" s="61"/>
+      <c r="W6" s="61"/>
+      <c r="X6" s="62"/>
+    </row>
+    <row r="7" spans="1:24" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
-      <c r="D7" s="95"/>
-      <c r="E7" s="96"/>
-      <c r="F7" s="96"/>
-      <c r="G7" s="96"/>
-      <c r="H7" s="96"/>
-      <c r="I7" s="96"/>
-      <c r="J7" s="96"/>
-      <c r="K7" s="96"/>
-      <c r="L7" s="96"/>
-      <c r="M7" s="96"/>
-      <c r="N7" s="96"/>
-      <c r="O7" s="96"/>
-      <c r="P7" s="97"/>
-      <c r="Q7" s="95" t="s">
+      <c r="D7" s="60"/>
+      <c r="E7" s="61"/>
+      <c r="F7" s="61"/>
+      <c r="G7" s="61"/>
+      <c r="H7" s="61"/>
+      <c r="I7" s="61"/>
+      <c r="J7" s="61"/>
+      <c r="K7" s="61"/>
+      <c r="L7" s="61"/>
+      <c r="M7" s="61"/>
+      <c r="N7" s="61"/>
+      <c r="O7" s="61"/>
+      <c r="P7" s="62"/>
+      <c r="Q7" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="R7" s="96"/>
-      <c r="S7" s="97"/>
-      <c r="T7" s="95"/>
-      <c r="U7" s="96"/>
-      <c r="V7" s="96"/>
-      <c r="W7" s="96"/>
-      <c r="X7" s="97"/>
-    </row>
-    <row r="8" spans="1:24" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="94" t="s">
+      <c r="R7" s="61"/>
+      <c r="S7" s="62"/>
+      <c r="T7" s="60"/>
+      <c r="U7" s="61"/>
+      <c r="V7" s="61"/>
+      <c r="W7" s="61"/>
+      <c r="X7" s="62"/>
+    </row>
+    <row r="8" spans="1:24" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="94"/>
-      <c r="C8" s="94"/>
-      <c r="D8" s="95"/>
-      <c r="E8" s="96"/>
-      <c r="F8" s="96"/>
-      <c r="G8" s="96"/>
-      <c r="H8" s="96"/>
-      <c r="I8" s="96"/>
-      <c r="J8" s="96"/>
-      <c r="K8" s="96"/>
-      <c r="L8" s="96"/>
-      <c r="M8" s="96"/>
-      <c r="N8" s="96"/>
-      <c r="O8" s="96"/>
-      <c r="P8" s="96"/>
-      <c r="Q8" s="96"/>
-      <c r="R8" s="96"/>
-      <c r="S8" s="96"/>
-      <c r="T8" s="96"/>
-      <c r="U8" s="96"/>
-      <c r="V8" s="96"/>
-      <c r="W8" s="96"/>
-      <c r="X8" s="97"/>
-    </row>
-    <row r="9" spans="1:24" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="100" t="s">
+      <c r="B8" s="63"/>
+      <c r="C8" s="63"/>
+      <c r="D8" s="60"/>
+      <c r="E8" s="61"/>
+      <c r="F8" s="61"/>
+      <c r="G8" s="61"/>
+      <c r="H8" s="61"/>
+      <c r="I8" s="61"/>
+      <c r="J8" s="61"/>
+      <c r="K8" s="61"/>
+      <c r="L8" s="61"/>
+      <c r="M8" s="61"/>
+      <c r="N8" s="61"/>
+      <c r="O8" s="61"/>
+      <c r="P8" s="61"/>
+      <c r="Q8" s="61"/>
+      <c r="R8" s="61"/>
+      <c r="S8" s="61"/>
+      <c r="T8" s="61"/>
+      <c r="U8" s="61"/>
+      <c r="V8" s="61"/>
+      <c r="W8" s="61"/>
+      <c r="X8" s="62"/>
+    </row>
+    <row r="9" spans="1:24" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="101"/>
-      <c r="C9" s="101"/>
-      <c r="D9" s="101"/>
-      <c r="E9" s="102"/>
-      <c r="F9" s="95"/>
-      <c r="G9" s="96"/>
-      <c r="H9" s="96"/>
-      <c r="I9" s="96"/>
-      <c r="J9" s="96"/>
-      <c r="K9" s="96"/>
-      <c r="L9" s="96"/>
-      <c r="M9" s="96"/>
-      <c r="N9" s="96"/>
-      <c r="O9" s="96"/>
-      <c r="P9" s="96"/>
-      <c r="Q9" s="97"/>
-      <c r="R9" s="95" t="s">
+      <c r="B9" s="68"/>
+      <c r="C9" s="68"/>
+      <c r="D9" s="68"/>
+      <c r="E9" s="69"/>
+      <c r="F9" s="60"/>
+      <c r="G9" s="61"/>
+      <c r="H9" s="61"/>
+      <c r="I9" s="61"/>
+      <c r="J9" s="61"/>
+      <c r="K9" s="61"/>
+      <c r="L9" s="61"/>
+      <c r="M9" s="61"/>
+      <c r="N9" s="61"/>
+      <c r="O9" s="61"/>
+      <c r="P9" s="61"/>
+      <c r="Q9" s="62"/>
+      <c r="R9" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="S9" s="97"/>
-      <c r="T9" s="95"/>
-      <c r="U9" s="96"/>
-      <c r="V9" s="96"/>
-      <c r="W9" s="96"/>
-      <c r="X9" s="97"/>
-    </row>
-    <row r="10" spans="1:24" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="100" t="s">
+      <c r="S9" s="62"/>
+      <c r="T9" s="60"/>
+      <c r="U9" s="61"/>
+      <c r="V9" s="61"/>
+      <c r="W9" s="61"/>
+      <c r="X9" s="62"/>
+    </row>
+    <row r="10" spans="1:24" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="67" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="101"/>
-      <c r="C10" s="102"/>
-      <c r="D10" s="95"/>
-      <c r="E10" s="96"/>
-      <c r="F10" s="96"/>
-      <c r="G10" s="96"/>
-      <c r="H10" s="96"/>
-      <c r="I10" s="96"/>
-      <c r="J10" s="96"/>
-      <c r="K10" s="96"/>
-      <c r="L10" s="96"/>
-      <c r="M10" s="96"/>
-      <c r="N10" s="96"/>
-      <c r="O10" s="96"/>
-      <c r="P10" s="97"/>
-      <c r="Q10" s="95" t="s">
+      <c r="B10" s="68"/>
+      <c r="C10" s="69"/>
+      <c r="D10" s="60"/>
+      <c r="E10" s="61"/>
+      <c r="F10" s="61"/>
+      <c r="G10" s="61"/>
+      <c r="H10" s="61"/>
+      <c r="I10" s="61"/>
+      <c r="J10" s="61"/>
+      <c r="K10" s="61"/>
+      <c r="L10" s="61"/>
+      <c r="M10" s="61"/>
+      <c r="N10" s="61"/>
+      <c r="O10" s="61"/>
+      <c r="P10" s="62"/>
+      <c r="Q10" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="R10" s="96"/>
-      <c r="S10" s="97"/>
-      <c r="T10" s="95"/>
-      <c r="U10" s="96"/>
-      <c r="V10" s="96"/>
-      <c r="W10" s="96"/>
-      <c r="X10" s="97"/>
-    </row>
-    <row r="11" spans="1:24" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="94" t="s">
+      <c r="R10" s="61"/>
+      <c r="S10" s="62"/>
+      <c r="T10" s="60"/>
+      <c r="U10" s="61"/>
+      <c r="V10" s="61"/>
+      <c r="W10" s="61"/>
+      <c r="X10" s="62"/>
+    </row>
+    <row r="11" spans="1:24" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="94"/>
-      <c r="C11" s="94"/>
-      <c r="D11" s="95"/>
-      <c r="E11" s="96"/>
-      <c r="F11" s="96"/>
-      <c r="G11" s="96"/>
-      <c r="H11" s="96"/>
-      <c r="I11" s="96"/>
-      <c r="J11" s="96"/>
-      <c r="K11" s="96"/>
-      <c r="L11" s="96"/>
-      <c r="M11" s="96"/>
-      <c r="N11" s="96"/>
-      <c r="O11" s="96"/>
-      <c r="P11" s="96"/>
-      <c r="Q11" s="96"/>
-      <c r="R11" s="96"/>
-      <c r="S11" s="96"/>
-      <c r="T11" s="96"/>
-      <c r="U11" s="96"/>
-      <c r="V11" s="96"/>
-      <c r="W11" s="96"/>
-      <c r="X11" s="97"/>
-    </row>
-    <row r="12" spans="1:24" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="68" t="s">
+      <c r="B11" s="63"/>
+      <c r="C11" s="63"/>
+      <c r="D11" s="60"/>
+      <c r="E11" s="61"/>
+      <c r="F11" s="61"/>
+      <c r="G11" s="61"/>
+      <c r="H11" s="61"/>
+      <c r="I11" s="61"/>
+      <c r="J11" s="61"/>
+      <c r="K11" s="61"/>
+      <c r="L11" s="61"/>
+      <c r="M11" s="61"/>
+      <c r="N11" s="61"/>
+      <c r="O11" s="61"/>
+      <c r="P11" s="61"/>
+      <c r="Q11" s="61"/>
+      <c r="R11" s="61"/>
+      <c r="S11" s="61"/>
+      <c r="T11" s="61"/>
+      <c r="U11" s="61"/>
+      <c r="V11" s="61"/>
+      <c r="W11" s="61"/>
+      <c r="X11" s="62"/>
+    </row>
+    <row r="12" spans="1:24" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="64" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="69"/>
-      <c r="C12" s="69"/>
-      <c r="D12" s="69"/>
-      <c r="E12" s="69"/>
-      <c r="F12" s="69"/>
-      <c r="G12" s="69"/>
-      <c r="H12" s="69"/>
-      <c r="I12" s="69"/>
-      <c r="J12" s="69"/>
-      <c r="K12" s="69"/>
-      <c r="L12" s="69"/>
-      <c r="M12" s="69"/>
-      <c r="N12" s="69"/>
-      <c r="O12" s="69"/>
-      <c r="P12" s="69"/>
-      <c r="Q12" s="69"/>
-      <c r="R12" s="69"/>
-      <c r="S12" s="69"/>
-      <c r="T12" s="69"/>
-      <c r="U12" s="69"/>
-      <c r="V12" s="69"/>
-      <c r="W12" s="69"/>
-      <c r="X12" s="98"/>
-    </row>
-    <row r="13" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="83" t="s">
+      <c r="B12" s="65"/>
+      <c r="C12" s="65"/>
+      <c r="D12" s="65"/>
+      <c r="E12" s="65"/>
+      <c r="F12" s="65"/>
+      <c r="G12" s="65"/>
+      <c r="H12" s="65"/>
+      <c r="I12" s="65"/>
+      <c r="J12" s="65"/>
+      <c r="K12" s="65"/>
+      <c r="L12" s="65"/>
+      <c r="M12" s="65"/>
+      <c r="N12" s="65"/>
+      <c r="O12" s="65"/>
+      <c r="P12" s="65"/>
+      <c r="Q12" s="65"/>
+      <c r="R12" s="65"/>
+      <c r="S12" s="65"/>
+      <c r="T12" s="65"/>
+      <c r="U12" s="65"/>
+      <c r="V12" s="65"/>
+      <c r="W12" s="65"/>
+      <c r="X12" s="66"/>
+    </row>
+    <row r="13" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="83"/>
-      <c r="C13" s="83"/>
-      <c r="D13" s="83"/>
-      <c r="E13" s="83"/>
-      <c r="F13" s="83"/>
+      <c r="B13" s="70"/>
+      <c r="C13" s="70"/>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
       <c r="G13" s="2"/>
-      <c r="H13" s="83" t="s">
+      <c r="H13" s="70" t="s">
         <v>15</v>
       </c>
-      <c r="I13" s="83"/>
-      <c r="J13" s="83"/>
-      <c r="K13" s="83"/>
-      <c r="L13" s="83"/>
-      <c r="M13" s="83"/>
-      <c r="N13" s="83"/>
-      <c r="O13" s="84"/>
+      <c r="I13" s="70"/>
+      <c r="J13" s="70"/>
+      <c r="K13" s="70"/>
+      <c r="L13" s="70"/>
+      <c r="M13" s="70"/>
+      <c r="N13" s="70"/>
+      <c r="O13" s="71"/>
       <c r="P13" s="2"/>
-      <c r="Q13" s="99" t="s">
+      <c r="Q13" s="72" t="s">
         <v>16</v>
       </c>
-      <c r="R13" s="83"/>
-      <c r="S13" s="83"/>
-      <c r="T13" s="83"/>
-      <c r="U13" s="83"/>
-      <c r="V13" s="83"/>
-      <c r="W13" s="83"/>
+      <c r="R13" s="70"/>
+      <c r="S13" s="70"/>
+      <c r="T13" s="70"/>
+      <c r="U13" s="70"/>
+      <c r="V13" s="70"/>
+      <c r="W13" s="70"/>
       <c r="X13" s="2"/>
     </row>
-    <row r="14" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="79" t="s">
+    <row r="14" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="79"/>
-      <c r="C14" s="79"/>
-      <c r="D14" s="79"/>
-      <c r="E14" s="79"/>
-      <c r="F14" s="79"/>
+      <c r="B14" s="73"/>
+      <c r="C14" s="73"/>
+      <c r="D14" s="73"/>
+      <c r="E14" s="73"/>
+      <c r="F14" s="73"/>
       <c r="G14" s="3"/>
-      <c r="H14" s="79" t="s">
+      <c r="H14" s="73" t="s">
         <v>18</v>
       </c>
-      <c r="I14" s="79"/>
-      <c r="J14" s="79"/>
-      <c r="K14" s="79"/>
-      <c r="L14" s="79"/>
-      <c r="M14" s="79"/>
-      <c r="N14" s="79"/>
-      <c r="O14" s="77"/>
+      <c r="I14" s="73"/>
+      <c r="J14" s="73"/>
+      <c r="K14" s="73"/>
+      <c r="L14" s="73"/>
+      <c r="M14" s="73"/>
+      <c r="N14" s="73"/>
+      <c r="O14" s="74"/>
       <c r="P14" s="3"/>
-      <c r="Q14" s="78" t="s">
+      <c r="Q14" s="75" t="s">
         <v>19</v>
       </c>
-      <c r="R14" s="79"/>
-      <c r="S14" s="79"/>
-      <c r="T14" s="79"/>
-      <c r="U14" s="79"/>
-      <c r="V14" s="79"/>
-      <c r="W14" s="79"/>
+      <c r="R14" s="73"/>
+      <c r="S14" s="73"/>
+      <c r="T14" s="73"/>
+      <c r="U14" s="73"/>
+      <c r="V14" s="73"/>
+      <c r="W14" s="73"/>
       <c r="X14" s="3"/>
     </row>
-    <row r="15" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="79" t="s">
+    <row r="15" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="79"/>
-      <c r="C15" s="79"/>
-      <c r="D15" s="79"/>
-      <c r="E15" s="79"/>
-      <c r="F15" s="79"/>
+      <c r="B15" s="73"/>
+      <c r="C15" s="73"/>
+      <c r="D15" s="73"/>
+      <c r="E15" s="73"/>
+      <c r="F15" s="73"/>
       <c r="G15" s="3"/>
-      <c r="H15" s="74" t="s">
+      <c r="H15" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="I15" s="75"/>
-      <c r="J15" s="75"/>
-      <c r="K15" s="75"/>
-      <c r="L15" s="75"/>
-      <c r="M15" s="75"/>
-      <c r="N15" s="75"/>
-      <c r="O15" s="76"/>
+      <c r="I15" s="79"/>
+      <c r="J15" s="79"/>
+      <c r="K15" s="79"/>
+      <c r="L15" s="79"/>
+      <c r="M15" s="79"/>
+      <c r="N15" s="79"/>
+      <c r="O15" s="80"/>
       <c r="P15" s="3"/>
-      <c r="Q15" s="78" t="s">
+      <c r="Q15" s="75" t="s">
         <v>22</v>
       </c>
-      <c r="R15" s="79"/>
-      <c r="S15" s="79"/>
-      <c r="T15" s="79"/>
-      <c r="U15" s="79"/>
-      <c r="V15" s="79"/>
-      <c r="W15" s="79"/>
+      <c r="R15" s="73"/>
+      <c r="S15" s="73"/>
+      <c r="T15" s="73"/>
+      <c r="U15" s="73"/>
+      <c r="V15" s="73"/>
+      <c r="W15" s="73"/>
       <c r="X15" s="3"/>
     </row>
-    <row r="16" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="79" t="s">
+    <row r="16" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="79"/>
-      <c r="C16" s="79"/>
-      <c r="D16" s="79"/>
-      <c r="E16" s="79"/>
-      <c r="F16" s="79"/>
+      <c r="B16" s="73"/>
+      <c r="C16" s="73"/>
+      <c r="D16" s="73"/>
+      <c r="E16" s="73"/>
+      <c r="F16" s="73"/>
       <c r="G16" s="3"/>
-      <c r="H16" s="83" t="s">
+      <c r="H16" s="70" t="s">
         <v>24</v>
       </c>
-      <c r="I16" s="83"/>
-      <c r="J16" s="83"/>
-      <c r="K16" s="83"/>
-      <c r="L16" s="83"/>
-      <c r="M16" s="83"/>
-      <c r="N16" s="83"/>
-      <c r="O16" s="84"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="70"/>
+      <c r="K16" s="70"/>
+      <c r="L16" s="70"/>
+      <c r="M16" s="70"/>
+      <c r="N16" s="70"/>
+      <c r="O16" s="71"/>
       <c r="P16" s="3"/>
-      <c r="Q16" s="78" t="s">
+      <c r="Q16" s="75" t="s">
         <v>25</v>
       </c>
-      <c r="R16" s="79"/>
-      <c r="S16" s="79"/>
-      <c r="T16" s="79"/>
-      <c r="U16" s="79"/>
-      <c r="V16" s="79"/>
-      <c r="W16" s="79"/>
+      <c r="R16" s="73"/>
+      <c r="S16" s="73"/>
+      <c r="T16" s="73"/>
+      <c r="U16" s="73"/>
+      <c r="V16" s="73"/>
+      <c r="W16" s="73"/>
       <c r="X16" s="3"/>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>26</v>
       </c>
@@ -1939,7 +1951,7 @@
       <c r="W17" s="7"/>
       <c r="X17" s="8"/>
     </row>
-    <row r="18" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="9"/>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
@@ -1965,7 +1977,7 @@
       <c r="W18" s="11"/>
       <c r="X18" s="12"/>
     </row>
-    <row r="19" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="9"/>
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
@@ -1991,7 +2003,7 @@
       <c r="W19" s="11"/>
       <c r="X19" s="12"/>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A20" s="9"/>
       <c r="B20" s="10"/>
       <c r="C20" s="10"/>
@@ -2017,7 +2029,7 @@
       <c r="W20" s="11"/>
       <c r="X20" s="12"/>
     </row>
-    <row r="21" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:24" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13"/>
       <c r="B21" s="14"/>
       <c r="C21" s="14"/>
@@ -2043,7 +2055,7 @@
       <c r="W21" s="14"/>
       <c r="X21" s="15"/>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>27</v>
       </c>
@@ -2071,7 +2083,7 @@
       <c r="W22" s="7"/>
       <c r="X22" s="8"/>
     </row>
-    <row r="23" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:24" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="17"/>
       <c r="B23" s="18"/>
       <c r="C23" s="18"/>
@@ -2097,39 +2109,39 @@
       <c r="W23" s="18"/>
       <c r="X23" s="19"/>
     </row>
-    <row r="24" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="85" t="s">
+    <row r="24" spans="1:24" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="82" t="s">
         <v>28</v>
       </c>
-      <c r="B24" s="86"/>
-      <c r="C24" s="86"/>
-      <c r="D24" s="86"/>
-      <c r="E24" s="87"/>
-      <c r="F24" s="88"/>
-      <c r="G24" s="89"/>
-      <c r="H24" s="89"/>
-      <c r="I24" s="89"/>
-      <c r="J24" s="89"/>
-      <c r="K24" s="89"/>
-      <c r="L24" s="89"/>
-      <c r="M24" s="89"/>
-      <c r="N24" s="89"/>
-      <c r="O24" s="89"/>
-      <c r="P24" s="89"/>
-      <c r="Q24" s="90"/>
-      <c r="R24" s="91" t="s">
+      <c r="B24" s="83"/>
+      <c r="C24" s="83"/>
+      <c r="D24" s="83"/>
+      <c r="E24" s="84"/>
+      <c r="F24" s="85"/>
+      <c r="G24" s="86"/>
+      <c r="H24" s="86"/>
+      <c r="I24" s="86"/>
+      <c r="J24" s="86"/>
+      <c r="K24" s="86"/>
+      <c r="L24" s="86"/>
+      <c r="M24" s="86"/>
+      <c r="N24" s="86"/>
+      <c r="O24" s="86"/>
+      <c r="P24" s="86"/>
+      <c r="Q24" s="87"/>
+      <c r="R24" s="88" t="s">
         <v>29</v>
       </c>
-      <c r="S24" s="92"/>
-      <c r="T24" s="93"/>
+      <c r="S24" s="89"/>
+      <c r="T24" s="90"/>
       <c r="U24" s="20"/>
-      <c r="V24" s="91" t="s">
+      <c r="V24" s="88" t="s">
         <v>30</v>
       </c>
-      <c r="W24" s="93"/>
+      <c r="W24" s="90"/>
       <c r="X24" s="20"/>
     </row>
-    <row r="25" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="21" t="s">
         <v>31</v>
       </c>
@@ -2152,14 +2164,14 @@
       <c r="R25" s="23"/>
       <c r="S25" s="23"/>
       <c r="T25" s="23"/>
-      <c r="U25" s="53" t="s">
+      <c r="U25" s="52" t="s">
         <v>32</v>
       </c>
       <c r="V25" s="22"/>
       <c r="W25" s="22"/>
       <c r="X25" s="24"/>
     </row>
-    <row r="26" spans="1:24" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:24" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="25"/>
       <c r="B26" s="26"/>
       <c r="C26" s="26"/>
@@ -2180,14 +2192,14 @@
       <c r="R26" s="26"/>
       <c r="S26" s="26"/>
       <c r="T26" s="26"/>
-      <c r="U26" s="54" t="s">
+      <c r="U26" s="53" t="s">
         <v>33</v>
       </c>
       <c r="V26" s="26"/>
       <c r="W26" s="26"/>
       <c r="X26" s="27"/>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27" s="17" t="s">
         <v>34</v>
       </c>
@@ -2215,7 +2227,7 @@
       <c r="W27" s="7"/>
       <c r="X27" s="8"/>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28" s="9"/>
       <c r="B28" s="10"/>
       <c r="C28" s="10"/>
@@ -2241,7 +2253,7 @@
       <c r="W28" s="11"/>
       <c r="X28" s="12"/>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A29" s="9"/>
       <c r="B29" s="10"/>
       <c r="C29" s="10"/>
@@ -2267,7 +2279,7 @@
       <c r="W29" s="11"/>
       <c r="X29" s="12"/>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A30" s="9"/>
       <c r="B30" s="10"/>
       <c r="C30" s="10"/>
@@ -2293,7 +2305,7 @@
       <c r="W30" s="11"/>
       <c r="X30" s="12"/>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A31" s="29"/>
       <c r="B31" s="30"/>
       <c r="C31" s="30"/>
@@ -2319,7 +2331,7 @@
       <c r="W31" s="30"/>
       <c r="X31" s="31"/>
     </row>
-    <row r="32" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:24" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A32" s="21"/>
       <c r="B32" s="22"/>
       <c r="C32" s="22"/>
@@ -2345,191 +2357,191 @@
       <c r="W32" s="22"/>
       <c r="X32" s="24"/>
     </row>
-    <row r="33" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="73" t="s">
+    <row r="33" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="91" t="s">
         <v>35</v>
       </c>
-      <c r="B33" s="70"/>
-      <c r="C33" s="70"/>
-      <c r="D33" s="70"/>
-      <c r="E33" s="70"/>
-      <c r="F33" s="70"/>
-      <c r="G33" s="70"/>
-      <c r="H33" s="70"/>
-      <c r="I33" s="70"/>
-      <c r="J33" s="70"/>
-      <c r="K33" s="70"/>
-      <c r="L33" s="70"/>
-      <c r="M33" s="70"/>
-      <c r="N33" s="70"/>
-      <c r="O33" s="70"/>
-      <c r="P33" s="70"/>
-      <c r="Q33" s="70"/>
-      <c r="R33" s="70"/>
-      <c r="S33" s="70"/>
-      <c r="T33" s="70"/>
-      <c r="U33" s="70"/>
-      <c r="V33" s="70"/>
-      <c r="W33" s="70"/>
-      <c r="X33" s="71"/>
-    </row>
-    <row r="34" spans="1:24" s="32" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="80" t="s">
+      <c r="B33" s="92"/>
+      <c r="C33" s="92"/>
+      <c r="D33" s="92"/>
+      <c r="E33" s="92"/>
+      <c r="F33" s="92"/>
+      <c r="G33" s="92"/>
+      <c r="H33" s="92"/>
+      <c r="I33" s="92"/>
+      <c r="J33" s="92"/>
+      <c r="K33" s="92"/>
+      <c r="L33" s="92"/>
+      <c r="M33" s="92"/>
+      <c r="N33" s="92"/>
+      <c r="O33" s="92"/>
+      <c r="P33" s="92"/>
+      <c r="Q33" s="92"/>
+      <c r="R33" s="92"/>
+      <c r="S33" s="92"/>
+      <c r="T33" s="92"/>
+      <c r="U33" s="92"/>
+      <c r="V33" s="92"/>
+      <c r="W33" s="92"/>
+      <c r="X33" s="93"/>
+    </row>
+    <row r="34" spans="1:24" s="32" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="76" t="s">
         <v>36</v>
       </c>
-      <c r="B34" s="81"/>
-      <c r="C34" s="81"/>
-      <c r="D34" s="81"/>
-      <c r="E34" s="82"/>
+      <c r="B34" s="77"/>
+      <c r="C34" s="77"/>
+      <c r="D34" s="77"/>
+      <c r="E34" s="78"/>
       <c r="F34" s="3"/>
-      <c r="G34" s="77" t="s">
+      <c r="G34" s="74" t="s">
         <v>37</v>
       </c>
-      <c r="H34" s="75"/>
-      <c r="I34" s="75"/>
-      <c r="J34" s="75"/>
-      <c r="K34" s="75"/>
-      <c r="L34" s="75"/>
-      <c r="M34" s="75"/>
-      <c r="N34" s="75"/>
-      <c r="O34" s="76"/>
+      <c r="H34" s="79"/>
+      <c r="I34" s="79"/>
+      <c r="J34" s="79"/>
+      <c r="K34" s="79"/>
+      <c r="L34" s="79"/>
+      <c r="M34" s="79"/>
+      <c r="N34" s="79"/>
+      <c r="O34" s="80"/>
       <c r="P34" s="3"/>
-      <c r="Q34" s="74" t="s">
+      <c r="Q34" s="81" t="s">
         <v>38</v>
       </c>
-      <c r="R34" s="75"/>
-      <c r="S34" s="75"/>
-      <c r="T34" s="75"/>
-      <c r="U34" s="75"/>
-      <c r="V34" s="75"/>
-      <c r="W34" s="78"/>
+      <c r="R34" s="79"/>
+      <c r="S34" s="79"/>
+      <c r="T34" s="79"/>
+      <c r="U34" s="79"/>
+      <c r="V34" s="79"/>
+      <c r="W34" s="75"/>
       <c r="X34" s="3"/>
     </row>
-    <row r="35" spans="1:24" s="32" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="74" t="s">
+    <row r="35" spans="1:24" s="32" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="81" t="s">
         <v>39</v>
       </c>
-      <c r="B35" s="75"/>
-      <c r="C35" s="75"/>
-      <c r="D35" s="75"/>
-      <c r="E35" s="76"/>
+      <c r="B35" s="79"/>
+      <c r="C35" s="79"/>
+      <c r="D35" s="79"/>
+      <c r="E35" s="80"/>
       <c r="F35" s="3"/>
-      <c r="G35" s="77" t="s">
+      <c r="G35" s="74" t="s">
         <v>40</v>
       </c>
-      <c r="H35" s="75"/>
-      <c r="I35" s="75"/>
-      <c r="J35" s="75"/>
-      <c r="K35" s="75"/>
-      <c r="L35" s="75"/>
-      <c r="M35" s="75"/>
-      <c r="N35" s="75"/>
-      <c r="O35" s="76"/>
+      <c r="H35" s="79"/>
+      <c r="I35" s="79"/>
+      <c r="J35" s="79"/>
+      <c r="K35" s="79"/>
+      <c r="L35" s="79"/>
+      <c r="M35" s="79"/>
+      <c r="N35" s="79"/>
+      <c r="O35" s="80"/>
       <c r="P35" s="3"/>
-      <c r="Q35" s="74" t="s">
+      <c r="Q35" s="81" t="s">
         <v>41</v>
       </c>
-      <c r="R35" s="75"/>
-      <c r="S35" s="75"/>
-      <c r="T35" s="75"/>
-      <c r="U35" s="75"/>
-      <c r="V35" s="75"/>
-      <c r="W35" s="78"/>
+      <c r="R35" s="79"/>
+      <c r="S35" s="79"/>
+      <c r="T35" s="79"/>
+      <c r="U35" s="79"/>
+      <c r="V35" s="79"/>
+      <c r="W35" s="75"/>
       <c r="X35" s="3"/>
     </row>
-    <row r="36" spans="1:24" s="32" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="74" t="s">
+    <row r="36" spans="1:24" s="32" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="81" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="75"/>
-      <c r="C36" s="75"/>
-      <c r="D36" s="75"/>
-      <c r="E36" s="76"/>
+      <c r="B36" s="79"/>
+      <c r="C36" s="79"/>
+      <c r="D36" s="79"/>
+      <c r="E36" s="80"/>
       <c r="F36" s="3"/>
-      <c r="G36" s="77" t="s">
+      <c r="G36" s="74" t="s">
         <v>43</v>
       </c>
-      <c r="H36" s="75"/>
-      <c r="I36" s="75"/>
-      <c r="J36" s="75"/>
-      <c r="K36" s="75"/>
-      <c r="L36" s="75"/>
-      <c r="M36" s="75"/>
-      <c r="N36" s="75"/>
-      <c r="O36" s="76"/>
+      <c r="H36" s="79"/>
+      <c r="I36" s="79"/>
+      <c r="J36" s="79"/>
+      <c r="K36" s="79"/>
+      <c r="L36" s="79"/>
+      <c r="M36" s="79"/>
+      <c r="N36" s="79"/>
+      <c r="O36" s="80"/>
       <c r="P36" s="3"/>
-      <c r="Q36" s="74" t="s">
+      <c r="Q36" s="81" t="s">
         <v>44</v>
       </c>
-      <c r="R36" s="75"/>
-      <c r="S36" s="75"/>
-      <c r="T36" s="75"/>
-      <c r="U36" s="75"/>
-      <c r="V36" s="75"/>
-      <c r="W36" s="78"/>
+      <c r="R36" s="79"/>
+      <c r="S36" s="79"/>
+      <c r="T36" s="79"/>
+      <c r="U36" s="79"/>
+      <c r="V36" s="79"/>
+      <c r="W36" s="75"/>
       <c r="X36" s="3"/>
     </row>
-    <row r="37" spans="1:24" s="32" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="62" t="s">
+    <row r="37" spans="1:24" s="32" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="95" t="s">
         <v>45</v>
       </c>
-      <c r="B37" s="63"/>
-      <c r="C37" s="63"/>
-      <c r="D37" s="63"/>
-      <c r="E37" s="64"/>
+      <c r="B37" s="96"/>
+      <c r="C37" s="96"/>
+      <c r="D37" s="96"/>
+      <c r="E37" s="97"/>
       <c r="F37" s="3"/>
-      <c r="G37" s="65" t="s">
+      <c r="G37" s="98" t="s">
         <v>46</v>
       </c>
-      <c r="H37" s="65"/>
-      <c r="I37" s="65"/>
-      <c r="J37" s="65"/>
-      <c r="K37" s="65"/>
-      <c r="L37" s="65"/>
-      <c r="M37" s="65"/>
-      <c r="N37" s="65"/>
-      <c r="O37" s="66"/>
+      <c r="H37" s="98"/>
+      <c r="I37" s="98"/>
+      <c r="J37" s="98"/>
+      <c r="K37" s="98"/>
+      <c r="L37" s="98"/>
+      <c r="M37" s="98"/>
+      <c r="N37" s="98"/>
+      <c r="O37" s="99"/>
       <c r="P37" s="3"/>
-      <c r="Q37" s="63" t="s">
+      <c r="Q37" s="96" t="s">
         <v>47</v>
       </c>
-      <c r="R37" s="63"/>
-      <c r="S37" s="63"/>
-      <c r="T37" s="63"/>
-      <c r="U37" s="63"/>
-      <c r="V37" s="63"/>
-      <c r="W37" s="67"/>
+      <c r="R37" s="96"/>
+      <c r="S37" s="96"/>
+      <c r="T37" s="96"/>
+      <c r="U37" s="96"/>
+      <c r="V37" s="96"/>
+      <c r="W37" s="100"/>
       <c r="X37" s="3"/>
     </row>
-    <row r="38" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="68" t="s">
+    <row r="38" spans="1:24" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="B38" s="69"/>
-      <c r="C38" s="69"/>
-      <c r="D38" s="69"/>
-      <c r="E38" s="69"/>
-      <c r="F38" s="69"/>
-      <c r="G38" s="69"/>
-      <c r="H38" s="69"/>
-      <c r="I38" s="69"/>
-      <c r="J38" s="69"/>
-      <c r="K38" s="69"/>
-      <c r="L38" s="69"/>
-      <c r="M38" s="69"/>
-      <c r="N38" s="69"/>
-      <c r="O38" s="69"/>
-      <c r="P38" s="69"/>
-      <c r="Q38" s="69"/>
-      <c r="R38" s="69"/>
-      <c r="S38" s="70"/>
-      <c r="T38" s="70"/>
-      <c r="U38" s="70"/>
-      <c r="V38" s="70"/>
-      <c r="W38" s="70"/>
-      <c r="X38" s="71"/>
-    </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="B38" s="65"/>
+      <c r="C38" s="65"/>
+      <c r="D38" s="65"/>
+      <c r="E38" s="65"/>
+      <c r="F38" s="65"/>
+      <c r="G38" s="65"/>
+      <c r="H38" s="65"/>
+      <c r="I38" s="65"/>
+      <c r="J38" s="65"/>
+      <c r="K38" s="65"/>
+      <c r="L38" s="65"/>
+      <c r="M38" s="65"/>
+      <c r="N38" s="65"/>
+      <c r="O38" s="65"/>
+      <c r="P38" s="65"/>
+      <c r="Q38" s="65"/>
+      <c r="R38" s="65"/>
+      <c r="S38" s="92"/>
+      <c r="T38" s="92"/>
+      <c r="U38" s="92"/>
+      <c r="V38" s="92"/>
+      <c r="W38" s="92"/>
+      <c r="X38" s="93"/>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A39" s="33"/>
       <c r="B39" s="34"/>
       <c r="C39" s="34"/>
@@ -2555,7 +2567,7 @@
       <c r="W39" s="34"/>
       <c r="X39" s="35"/>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A40" s="36"/>
       <c r="B40" s="37"/>
       <c r="C40" s="37"/>
@@ -2581,7 +2593,7 @@
       <c r="W40" s="37"/>
       <c r="X40" s="38"/>
     </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A41" s="36"/>
       <c r="B41" s="37"/>
       <c r="C41" s="37"/>
@@ -2607,7 +2619,7 @@
       <c r="W41" s="37"/>
       <c r="X41" s="38"/>
     </row>
-    <row r="42" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:24" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A42" s="39"/>
       <c r="B42" s="40"/>
       <c r="C42" s="40"/>
@@ -2633,175 +2645,175 @@
       <c r="W42" s="40"/>
       <c r="X42" s="41"/>
     </row>
-    <row r="43" spans="1:24" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="72"/>
-      <c r="B43" s="72"/>
-      <c r="C43" s="72"/>
-      <c r="D43" s="72"/>
-      <c r="E43" s="72"/>
-      <c r="F43" s="72"/>
-      <c r="G43" s="72"/>
-      <c r="H43" s="72"/>
-      <c r="I43" s="72"/>
-      <c r="J43" s="72"/>
-      <c r="K43" s="72"/>
-      <c r="L43" s="72"/>
-      <c r="M43" s="72"/>
-      <c r="N43" s="72"/>
-      <c r="O43" s="72"/>
-      <c r="P43" s="72"/>
-      <c r="Q43" s="72"/>
-      <c r="R43" s="72"/>
-      <c r="S43" s="72"/>
-      <c r="T43" s="72"/>
-      <c r="U43" s="72"/>
-      <c r="V43" s="72"/>
-      <c r="W43" s="72"/>
-      <c r="X43" s="72"/>
-    </row>
-    <row r="44" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="61" t="s">
+    <row r="43" spans="1:24" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="101"/>
+      <c r="B43" s="101"/>
+      <c r="C43" s="101"/>
+      <c r="D43" s="101"/>
+      <c r="E43" s="101"/>
+      <c r="F43" s="101"/>
+      <c r="G43" s="101"/>
+      <c r="H43" s="101"/>
+      <c r="I43" s="101"/>
+      <c r="J43" s="101"/>
+      <c r="K43" s="101"/>
+      <c r="L43" s="101"/>
+      <c r="M43" s="101"/>
+      <c r="N43" s="101"/>
+      <c r="O43" s="101"/>
+      <c r="P43" s="101"/>
+      <c r="Q43" s="101"/>
+      <c r="R43" s="101"/>
+      <c r="S43" s="101"/>
+      <c r="T43" s="101"/>
+      <c r="U43" s="101"/>
+      <c r="V43" s="101"/>
+      <c r="W43" s="101"/>
+      <c r="X43" s="101"/>
+    </row>
+    <row r="44" spans="1:24" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="94" t="s">
         <v>49</v>
       </c>
-      <c r="B44" s="61"/>
-      <c r="C44" s="61"/>
-      <c r="D44" s="61"/>
-      <c r="E44" s="61"/>
-      <c r="F44" s="61"/>
-      <c r="G44" s="61"/>
-      <c r="H44" s="61"/>
-      <c r="I44" s="61"/>
-      <c r="J44" s="61"/>
-      <c r="K44" s="61"/>
-      <c r="L44" s="61" t="s">
+      <c r="B44" s="94"/>
+      <c r="C44" s="94"/>
+      <c r="D44" s="94"/>
+      <c r="E44" s="94"/>
+      <c r="F44" s="94"/>
+      <c r="G44" s="94"/>
+      <c r="H44" s="94"/>
+      <c r="I44" s="94"/>
+      <c r="J44" s="94"/>
+      <c r="K44" s="94"/>
+      <c r="L44" s="94" t="s">
         <v>50</v>
       </c>
-      <c r="M44" s="61"/>
-      <c r="N44" s="61"/>
-      <c r="O44" s="61"/>
-      <c r="P44" s="61"/>
-      <c r="Q44" s="61"/>
-      <c r="R44" s="61"/>
-      <c r="S44" s="61"/>
-      <c r="T44" s="61"/>
-      <c r="U44" s="61"/>
-      <c r="V44" s="61"/>
-      <c r="W44" s="61"/>
-      <c r="X44" s="61"/>
-    </row>
-    <row r="45" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="55"/>
-      <c r="B45" s="55"/>
-      <c r="C45" s="55"/>
-      <c r="D45" s="55"/>
-      <c r="E45" s="55"/>
-      <c r="F45" s="55"/>
-      <c r="G45" s="55"/>
-      <c r="H45" s="55"/>
-      <c r="I45" s="55"/>
-      <c r="J45" s="55"/>
-      <c r="K45" s="55"/>
-      <c r="L45" s="55"/>
-      <c r="M45" s="55"/>
-      <c r="N45" s="55"/>
-      <c r="O45" s="55"/>
-      <c r="P45" s="55"/>
-      <c r="Q45" s="55"/>
-      <c r="R45" s="55"/>
-      <c r="S45" s="55"/>
-      <c r="T45" s="55"/>
-      <c r="U45" s="55"/>
-      <c r="V45" s="55"/>
-      <c r="W45" s="55"/>
-      <c r="X45" s="55"/>
-    </row>
-    <row r="46" spans="1:24" ht="20.100000000000001" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="56"/>
-      <c r="B46" s="56"/>
-      <c r="C46" s="56"/>
-      <c r="D46" s="56"/>
-      <c r="E46" s="56"/>
-      <c r="F46" s="56"/>
-      <c r="G46" s="56" t="s">
+      <c r="M44" s="94"/>
+      <c r="N44" s="94"/>
+      <c r="O44" s="94"/>
+      <c r="P44" s="94"/>
+      <c r="Q44" s="94"/>
+      <c r="R44" s="94"/>
+      <c r="S44" s="94"/>
+      <c r="T44" s="94"/>
+      <c r="U44" s="94"/>
+      <c r="V44" s="94"/>
+      <c r="W44" s="94"/>
+      <c r="X44" s="94"/>
+    </row>
+    <row r="45" spans="1:24" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="54"/>
+      <c r="B45" s="54"/>
+      <c r="C45" s="54"/>
+      <c r="D45" s="54"/>
+      <c r="E45" s="54"/>
+      <c r="F45" s="54"/>
+      <c r="G45" s="54"/>
+      <c r="H45" s="54"/>
+      <c r="I45" s="54"/>
+      <c r="J45" s="54"/>
+      <c r="K45" s="54"/>
+      <c r="L45" s="54"/>
+      <c r="M45" s="54"/>
+      <c r="N45" s="54"/>
+      <c r="O45" s="54"/>
+      <c r="P45" s="54"/>
+      <c r="Q45" s="54"/>
+      <c r="R45" s="54"/>
+      <c r="S45" s="54"/>
+      <c r="T45" s="54"/>
+      <c r="U45" s="54"/>
+      <c r="V45" s="54"/>
+      <c r="W45" s="54"/>
+      <c r="X45" s="54"/>
+    </row>
+    <row r="46" spans="1:24" ht="20" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="55"/>
+      <c r="B46" s="55"/>
+      <c r="C46" s="55"/>
+      <c r="D46" s="55"/>
+      <c r="E46" s="55"/>
+      <c r="F46" s="55"/>
+      <c r="G46" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="H46" s="56"/>
-      <c r="I46" s="56"/>
-      <c r="J46" s="56"/>
-      <c r="K46" s="56"/>
-      <c r="L46" s="56"/>
-      <c r="M46" s="56"/>
-      <c r="N46" s="56"/>
-      <c r="O46" s="56"/>
-      <c r="P46" s="56"/>
-      <c r="Q46" s="56"/>
-      <c r="R46" s="56"/>
-      <c r="S46" s="56"/>
-      <c r="T46" s="59" t="s">
+      <c r="H46" s="55"/>
+      <c r="I46" s="55"/>
+      <c r="J46" s="55"/>
+      <c r="K46" s="55"/>
+      <c r="L46" s="55"/>
+      <c r="M46" s="55"/>
+      <c r="N46" s="55"/>
+      <c r="O46" s="55"/>
+      <c r="P46" s="55"/>
+      <c r="Q46" s="55"/>
+      <c r="R46" s="55"/>
+      <c r="S46" s="55"/>
+      <c r="T46" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="U46" s="59"/>
-      <c r="V46" s="59"/>
-      <c r="W46" s="59"/>
-      <c r="X46" s="59"/>
-    </row>
-    <row r="47" spans="1:24" ht="20.100000000000001" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="57"/>
-      <c r="B47" s="57"/>
-      <c r="C47" s="57"/>
-      <c r="D47" s="57"/>
-      <c r="E47" s="57"/>
-      <c r="F47" s="57"/>
-      <c r="G47" s="57"/>
-      <c r="H47" s="57"/>
-      <c r="I47" s="57"/>
-      <c r="J47" s="57"/>
-      <c r="K47" s="57"/>
-      <c r="L47" s="57"/>
-      <c r="M47" s="57"/>
-      <c r="N47" s="57"/>
-      <c r="O47" s="57"/>
-      <c r="P47" s="57"/>
-      <c r="Q47" s="57"/>
-      <c r="R47" s="57"/>
-      <c r="S47" s="57"/>
-      <c r="T47" s="59" t="s">
+      <c r="U46" s="58"/>
+      <c r="V46" s="58"/>
+      <c r="W46" s="58"/>
+      <c r="X46" s="58"/>
+    </row>
+    <row r="47" spans="1:24" ht="20" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="56"/>
+      <c r="B47" s="56"/>
+      <c r="C47" s="56"/>
+      <c r="D47" s="56"/>
+      <c r="E47" s="56"/>
+      <c r="F47" s="56"/>
+      <c r="G47" s="56"/>
+      <c r="H47" s="56"/>
+      <c r="I47" s="56"/>
+      <c r="J47" s="56"/>
+      <c r="K47" s="56"/>
+      <c r="L47" s="56"/>
+      <c r="M47" s="56"/>
+      <c r="N47" s="56"/>
+      <c r="O47" s="56"/>
+      <c r="P47" s="56"/>
+      <c r="Q47" s="56"/>
+      <c r="R47" s="56"/>
+      <c r="S47" s="56"/>
+      <c r="T47" s="58" t="s">
         <v>52</v>
       </c>
-      <c r="U47" s="59"/>
-      <c r="V47" s="59"/>
-      <c r="W47" s="59"/>
-      <c r="X47" s="59"/>
-    </row>
-    <row r="48" spans="1:24" ht="20.100000000000001" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="58"/>
-      <c r="B48" s="58"/>
-      <c r="C48" s="58"/>
-      <c r="D48" s="58"/>
-      <c r="E48" s="58"/>
-      <c r="F48" s="58"/>
-      <c r="G48" s="58"/>
-      <c r="H48" s="58"/>
-      <c r="I48" s="58"/>
-      <c r="J48" s="58"/>
-      <c r="K48" s="58"/>
-      <c r="L48" s="58"/>
-      <c r="M48" s="58"/>
-      <c r="N48" s="58"/>
-      <c r="O48" s="58"/>
-      <c r="P48" s="58"/>
-      <c r="Q48" s="58"/>
-      <c r="R48" s="58"/>
-      <c r="S48" s="58"/>
-      <c r="T48" s="60" t="s">
+      <c r="U47" s="58"/>
+      <c r="V47" s="58"/>
+      <c r="W47" s="58"/>
+      <c r="X47" s="58"/>
+    </row>
+    <row r="48" spans="1:24" ht="20" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="57"/>
+      <c r="B48" s="57"/>
+      <c r="C48" s="57"/>
+      <c r="D48" s="57"/>
+      <c r="E48" s="57"/>
+      <c r="F48" s="57"/>
+      <c r="G48" s="57"/>
+      <c r="H48" s="57"/>
+      <c r="I48" s="57"/>
+      <c r="J48" s="57"/>
+      <c r="K48" s="57"/>
+      <c r="L48" s="57"/>
+      <c r="M48" s="57"/>
+      <c r="N48" s="57"/>
+      <c r="O48" s="57"/>
+      <c r="P48" s="57"/>
+      <c r="Q48" s="57"/>
+      <c r="R48" s="57"/>
+      <c r="S48" s="57"/>
+      <c r="T48" s="59" t="s">
         <v>53</v>
       </c>
-      <c r="U48" s="60"/>
-      <c r="V48" s="60"/>
-      <c r="W48" s="60"/>
-      <c r="X48" s="60"/>
-    </row>
-    <row r="49" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U48" s="59"/>
+      <c r="V48" s="59"/>
+      <c r="W48" s="59"/>
+      <c r="X48" s="59"/>
+    </row>
+    <row r="49" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="42" t="s">
         <v>51</v>
       </c>
@@ -2829,7 +2841,7 @@
       <c r="W49" s="44"/>
       <c r="X49" s="45"/>
     </row>
-    <row r="50" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="46"/>
       <c r="B50" s="47"/>
       <c r="C50" s="47"/>
@@ -2855,7 +2867,7 @@
       <c r="W50" s="47"/>
       <c r="X50" s="48"/>
     </row>
-    <row r="51" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="46"/>
       <c r="B51" s="47"/>
       <c r="C51" s="47"/>
@@ -2881,7 +2893,7 @@
       <c r="W51" s="47"/>
       <c r="X51" s="48"/>
     </row>
-    <row r="52" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="46"/>
       <c r="B52" s="47"/>
       <c r="C52" s="47"/>
@@ -2907,7 +2919,7 @@
       <c r="W52" s="47"/>
       <c r="X52" s="48"/>
     </row>
-    <row r="53" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="46"/>
       <c r="B53" s="47"/>
       <c r="C53" s="47"/>
@@ -2933,7 +2945,7 @@
       <c r="W53" s="47"/>
       <c r="X53" s="48"/>
     </row>
-    <row r="54" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="46"/>
       <c r="B54" s="47"/>
       <c r="C54" s="47"/>
@@ -2959,7 +2971,7 @@
       <c r="W54" s="47"/>
       <c r="X54" s="48"/>
     </row>
-    <row r="55" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="46"/>
       <c r="B55" s="47"/>
       <c r="C55" s="47"/>
@@ -2985,7 +2997,7 @@
       <c r="W55" s="47"/>
       <c r="X55" s="48"/>
     </row>
-    <row r="56" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="46"/>
       <c r="B56" s="47"/>
       <c r="C56" s="47"/>
@@ -3011,7 +3023,7 @@
       <c r="W56" s="47"/>
       <c r="X56" s="48"/>
     </row>
-    <row r="57" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="46"/>
       <c r="B57" s="47"/>
       <c r="C57" s="47"/>
@@ -3037,7 +3049,7 @@
       <c r="W57" s="47"/>
       <c r="X57" s="48"/>
     </row>
-    <row r="58" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="46"/>
       <c r="B58" s="47"/>
       <c r="C58" s="47"/>
@@ -3063,7 +3075,7 @@
       <c r="W58" s="47"/>
       <c r="X58" s="48"/>
     </row>
-    <row r="59" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="46"/>
       <c r="B59" s="47"/>
       <c r="C59" s="47"/>
@@ -3089,7 +3101,7 @@
       <c r="W59" s="47"/>
       <c r="X59" s="48"/>
     </row>
-    <row r="60" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="46"/>
       <c r="B60" s="47"/>
       <c r="C60" s="47"/>
@@ -3115,7 +3127,7 @@
       <c r="W60" s="47"/>
       <c r="X60" s="48"/>
     </row>
-    <row r="61" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="46"/>
       <c r="B61" s="47"/>
       <c r="C61" s="47"/>
@@ -3141,7 +3153,7 @@
       <c r="W61" s="47"/>
       <c r="X61" s="48"/>
     </row>
-    <row r="62" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="46"/>
       <c r="B62" s="47"/>
       <c r="C62" s="47"/>
@@ -3167,7 +3179,7 @@
       <c r="W62" s="47"/>
       <c r="X62" s="48"/>
     </row>
-    <row r="63" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="46"/>
       <c r="B63" s="47"/>
       <c r="C63" s="47"/>
@@ -3193,7 +3205,7 @@
       <c r="W63" s="47"/>
       <c r="X63" s="48"/>
     </row>
-    <row r="64" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="46"/>
       <c r="B64" s="47"/>
       <c r="C64" s="47"/>
@@ -3219,7 +3231,7 @@
       <c r="W64" s="47"/>
       <c r="X64" s="48"/>
     </row>
-    <row r="65" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="46"/>
       <c r="B65" s="47"/>
       <c r="C65" s="47"/>
@@ -3245,7 +3257,7 @@
       <c r="W65" s="47"/>
       <c r="X65" s="48"/>
     </row>
-    <row r="66" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="46"/>
       <c r="B66" s="47"/>
       <c r="C66" s="47"/>
@@ -3271,7 +3283,7 @@
       <c r="W66" s="47"/>
       <c r="X66" s="48"/>
     </row>
-    <row r="67" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="46"/>
       <c r="B67" s="47"/>
       <c r="C67" s="47"/>
@@ -3297,7 +3309,7 @@
       <c r="W67" s="47"/>
       <c r="X67" s="48"/>
     </row>
-    <row r="68" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="46"/>
       <c r="B68" s="47"/>
       <c r="C68" s="47"/>
@@ -3323,7 +3335,7 @@
       <c r="W68" s="47"/>
       <c r="X68" s="48"/>
     </row>
-    <row r="69" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="46"/>
       <c r="B69" s="47"/>
       <c r="C69" s="47"/>
@@ -3349,7 +3361,7 @@
       <c r="W69" s="47"/>
       <c r="X69" s="48"/>
     </row>
-    <row r="70" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="46"/>
       <c r="B70" s="47"/>
       <c r="C70" s="47"/>
@@ -3375,7 +3387,7 @@
       <c r="W70" s="47"/>
       <c r="X70" s="48"/>
     </row>
-    <row r="71" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="46"/>
       <c r="B71" s="47"/>
       <c r="C71" s="47"/>
@@ -3401,7 +3413,7 @@
       <c r="W71" s="47"/>
       <c r="X71" s="48"/>
     </row>
-    <row r="72" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="46"/>
       <c r="B72" s="47"/>
       <c r="C72" s="47"/>
@@ -3427,7 +3439,7 @@
       <c r="W72" s="47"/>
       <c r="X72" s="48"/>
     </row>
-    <row r="73" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="46"/>
       <c r="B73" s="47"/>
       <c r="C73" s="47"/>
@@ -3453,7 +3465,7 @@
       <c r="W73" s="47"/>
       <c r="X73" s="48"/>
     </row>
-    <row r="74" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="46"/>
       <c r="B74" s="47"/>
       <c r="C74" s="47"/>
@@ -3479,7 +3491,7 @@
       <c r="W74" s="47"/>
       <c r="X74" s="48"/>
     </row>
-    <row r="75" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="46"/>
       <c r="B75" s="47"/>
       <c r="C75" s="47"/>
@@ -3505,7 +3517,7 @@
       <c r="W75" s="47"/>
       <c r="X75" s="48"/>
     </row>
-    <row r="76" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="46"/>
       <c r="B76" s="47"/>
       <c r="C76" s="47"/>
@@ -3531,7 +3543,7 @@
       <c r="W76" s="47"/>
       <c r="X76" s="48"/>
     </row>
-    <row r="77" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="46"/>
       <c r="B77" s="47"/>
       <c r="C77" s="47"/>
@@ -3557,7 +3569,7 @@
       <c r="W77" s="47"/>
       <c r="X77" s="48"/>
     </row>
-    <row r="78" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="46"/>
       <c r="B78" s="47"/>
       <c r="C78" s="47"/>
@@ -3583,7 +3595,7 @@
       <c r="W78" s="47"/>
       <c r="X78" s="48"/>
     </row>
-    <row r="79" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="46"/>
       <c r="B79" s="47"/>
       <c r="C79" s="47"/>
@@ -3609,7 +3621,7 @@
       <c r="W79" s="47"/>
       <c r="X79" s="48"/>
     </row>
-    <row r="80" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="46"/>
       <c r="B80" s="47"/>
       <c r="C80" s="47"/>
@@ -3635,7 +3647,7 @@
       <c r="W80" s="47"/>
       <c r="X80" s="48"/>
     </row>
-    <row r="81" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="46"/>
       <c r="B81" s="47"/>
       <c r="C81" s="47"/>
@@ -3661,7 +3673,7 @@
       <c r="W81" s="47"/>
       <c r="X81" s="48"/>
     </row>
-    <row r="82" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="46"/>
       <c r="B82" s="47"/>
       <c r="C82" s="47"/>
@@ -3687,7 +3699,7 @@
       <c r="W82" s="47"/>
       <c r="X82" s="48"/>
     </row>
-    <row r="83" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="46"/>
       <c r="B83" s="47"/>
       <c r="C83" s="47"/>
@@ -3713,7 +3725,7 @@
       <c r="W83" s="47"/>
       <c r="X83" s="48"/>
     </row>
-    <row r="84" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="46"/>
       <c r="B84" s="47"/>
       <c r="C84" s="47"/>
@@ -3739,7 +3751,7 @@
       <c r="W84" s="47"/>
       <c r="X84" s="48"/>
     </row>
-    <row r="85" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:24" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A85" s="49"/>
       <c r="B85" s="50"/>
       <c r="C85" s="50"/>
@@ -3765,1471 +3777,28 @@
       <c r="W85" s="50"/>
       <c r="X85" s="51"/>
     </row>
-    <row r="86" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A86" s="52"/>
-      <c r="B86" s="52"/>
-      <c r="C86" s="52"/>
-      <c r="D86" s="52"/>
-      <c r="E86" s="52"/>
-      <c r="F86" s="52"/>
-      <c r="G86" s="52"/>
-      <c r="H86" s="52"/>
-      <c r="I86" s="52"/>
-      <c r="J86" s="52"/>
-      <c r="K86" s="52"/>
-      <c r="L86" s="52"/>
-      <c r="M86" s="52"/>
-      <c r="N86" s="52"/>
-      <c r="O86" s="52"/>
-      <c r="P86" s="52"/>
-      <c r="Q86" s="52"/>
-      <c r="R86" s="52"/>
-      <c r="S86" s="52"/>
-      <c r="T86" s="52"/>
-      <c r="U86" s="52"/>
-      <c r="V86" s="52"/>
-      <c r="W86" s="52"/>
-      <c r="X86" s="52"/>
-    </row>
-    <row r="87" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A87" s="52"/>
-      <c r="B87" s="52"/>
-      <c r="C87" s="52"/>
-      <c r="D87" s="52"/>
-      <c r="E87" s="52"/>
-      <c r="F87" s="52"/>
-      <c r="G87" s="52"/>
-      <c r="H87" s="52"/>
-      <c r="I87" s="52"/>
-      <c r="J87" s="52"/>
-      <c r="K87" s="52"/>
-      <c r="L87" s="52"/>
-      <c r="M87" s="52"/>
-      <c r="N87" s="52"/>
-      <c r="O87" s="52"/>
-      <c r="P87" s="52"/>
-      <c r="Q87" s="52"/>
-      <c r="R87" s="52"/>
-      <c r="S87" s="52"/>
-      <c r="T87" s="52"/>
-      <c r="U87" s="52"/>
-      <c r="V87" s="52"/>
-      <c r="W87" s="52"/>
-      <c r="X87" s="52"/>
-    </row>
-    <row r="88" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A88" s="52"/>
-      <c r="B88" s="52"/>
-      <c r="C88" s="52"/>
-      <c r="D88" s="52"/>
-      <c r="E88" s="52"/>
-      <c r="F88" s="52"/>
-      <c r="G88" s="52"/>
-      <c r="H88" s="52"/>
-      <c r="I88" s="52"/>
-      <c r="J88" s="52"/>
-      <c r="K88" s="52"/>
-      <c r="L88" s="52"/>
-      <c r="M88" s="52"/>
-      <c r="N88" s="52"/>
-      <c r="O88" s="52"/>
-      <c r="P88" s="52"/>
-      <c r="Q88" s="52"/>
-      <c r="R88" s="52"/>
-      <c r="S88" s="52"/>
-      <c r="T88" s="52"/>
-      <c r="U88" s="52"/>
-      <c r="V88" s="52"/>
-      <c r="W88" s="52"/>
-      <c r="X88" s="52"/>
-    </row>
-    <row r="89" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A89" s="52"/>
-      <c r="B89" s="52"/>
-      <c r="C89" s="52"/>
-      <c r="D89" s="52"/>
-      <c r="E89" s="52"/>
-      <c r="F89" s="52"/>
-      <c r="G89" s="52"/>
-      <c r="H89" s="52"/>
-      <c r="I89" s="52"/>
-      <c r="J89" s="52"/>
-      <c r="K89" s="52"/>
-      <c r="L89" s="52"/>
-      <c r="M89" s="52"/>
-      <c r="N89" s="52"/>
-      <c r="O89" s="52"/>
-      <c r="P89" s="52"/>
-      <c r="Q89" s="52"/>
-      <c r="R89" s="52"/>
-      <c r="S89" s="52"/>
-      <c r="T89" s="52"/>
-      <c r="U89" s="52"/>
-      <c r="V89" s="52"/>
-      <c r="W89" s="52"/>
-      <c r="X89" s="52"/>
-    </row>
-    <row r="90" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A90" s="52"/>
-      <c r="B90" s="52"/>
-      <c r="C90" s="52"/>
-      <c r="D90" s="52"/>
-      <c r="E90" s="52"/>
-      <c r="F90" s="52"/>
-      <c r="G90" s="52"/>
-      <c r="H90" s="52"/>
-      <c r="I90" s="52"/>
-      <c r="J90" s="52"/>
-      <c r="K90" s="52"/>
-      <c r="L90" s="52"/>
-      <c r="M90" s="52"/>
-      <c r="N90" s="52"/>
-      <c r="O90" s="52"/>
-      <c r="P90" s="52"/>
-      <c r="Q90" s="52"/>
-      <c r="R90" s="52"/>
-      <c r="S90" s="52"/>
-      <c r="T90" s="52"/>
-      <c r="U90" s="52"/>
-      <c r="V90" s="52"/>
-      <c r="W90" s="52"/>
-      <c r="X90" s="52"/>
-    </row>
-    <row r="91" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A91" s="52"/>
-      <c r="B91" s="52"/>
-      <c r="C91" s="52"/>
-      <c r="D91" s="52"/>
-      <c r="E91" s="52"/>
-      <c r="F91" s="52"/>
-      <c r="G91" s="52"/>
-      <c r="H91" s="52"/>
-      <c r="I91" s="52"/>
-      <c r="J91" s="52"/>
-      <c r="K91" s="52"/>
-      <c r="L91" s="52"/>
-      <c r="M91" s="52"/>
-      <c r="N91" s="52"/>
-      <c r="O91" s="52"/>
-      <c r="P91" s="52"/>
-      <c r="Q91" s="52"/>
-      <c r="R91" s="52"/>
-      <c r="S91" s="52"/>
-      <c r="T91" s="52"/>
-      <c r="U91" s="52"/>
-      <c r="V91" s="52"/>
-      <c r="W91" s="52"/>
-      <c r="X91" s="52"/>
-    </row>
-    <row r="92" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A92" s="52"/>
-      <c r="B92" s="52"/>
-      <c r="C92" s="52"/>
-      <c r="D92" s="52"/>
-      <c r="E92" s="52"/>
-      <c r="F92" s="52"/>
-      <c r="G92" s="52"/>
-      <c r="H92" s="52"/>
-      <c r="I92" s="52"/>
-      <c r="J92" s="52"/>
-      <c r="K92" s="52"/>
-      <c r="L92" s="52"/>
-      <c r="M92" s="52"/>
-      <c r="N92" s="52"/>
-      <c r="O92" s="52"/>
-      <c r="P92" s="52"/>
-      <c r="Q92" s="52"/>
-      <c r="R92" s="52"/>
-      <c r="S92" s="52"/>
-      <c r="T92" s="52"/>
-      <c r="U92" s="52"/>
-      <c r="V92" s="52"/>
-      <c r="W92" s="52"/>
-      <c r="X92" s="52"/>
-    </row>
-    <row r="93" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A93" s="52"/>
-      <c r="B93" s="52"/>
-      <c r="C93" s="52"/>
-      <c r="D93" s="52"/>
-      <c r="E93" s="52"/>
-      <c r="F93" s="52"/>
-      <c r="G93" s="52"/>
-      <c r="H93" s="52"/>
-      <c r="I93" s="52"/>
-      <c r="J93" s="52"/>
-      <c r="K93" s="52"/>
-      <c r="L93" s="52"/>
-      <c r="M93" s="52"/>
-      <c r="N93" s="52"/>
-      <c r="O93" s="52"/>
-      <c r="P93" s="52"/>
-      <c r="Q93" s="52"/>
-      <c r="R93" s="52"/>
-      <c r="S93" s="52"/>
-      <c r="T93" s="52"/>
-      <c r="U93" s="52"/>
-      <c r="V93" s="52"/>
-      <c r="W93" s="52"/>
-      <c r="X93" s="52"/>
-    </row>
-    <row r="94" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A94" s="52"/>
-      <c r="B94" s="52"/>
-      <c r="C94" s="52"/>
-      <c r="D94" s="52"/>
-      <c r="E94" s="52"/>
-      <c r="F94" s="52"/>
-      <c r="G94" s="52"/>
-      <c r="H94" s="52"/>
-      <c r="I94" s="52"/>
-      <c r="J94" s="52"/>
-      <c r="K94" s="52"/>
-      <c r="L94" s="52"/>
-      <c r="M94" s="52"/>
-      <c r="N94" s="52"/>
-      <c r="O94" s="52"/>
-      <c r="P94" s="52"/>
-      <c r="Q94" s="52"/>
-      <c r="R94" s="52"/>
-      <c r="S94" s="52"/>
-      <c r="T94" s="52"/>
-      <c r="U94" s="52"/>
-      <c r="V94" s="52"/>
-      <c r="W94" s="52"/>
-      <c r="X94" s="52"/>
-    </row>
-    <row r="95" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A95" s="52"/>
-      <c r="B95" s="52"/>
-      <c r="C95" s="52"/>
-      <c r="D95" s="52"/>
-      <c r="E95" s="52"/>
-      <c r="F95" s="52"/>
-      <c r="G95" s="52"/>
-      <c r="H95" s="52"/>
-      <c r="I95" s="52"/>
-      <c r="J95" s="52"/>
-      <c r="K95" s="52"/>
-      <c r="L95" s="52"/>
-      <c r="M95" s="52"/>
-      <c r="N95" s="52"/>
-      <c r="O95" s="52"/>
-      <c r="P95" s="52"/>
-      <c r="Q95" s="52"/>
-      <c r="R95" s="52"/>
-      <c r="S95" s="52"/>
-      <c r="T95" s="52"/>
-      <c r="U95" s="52"/>
-      <c r="V95" s="52"/>
-      <c r="W95" s="52"/>
-      <c r="X95" s="52"/>
-    </row>
-    <row r="96" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A96" s="52"/>
-      <c r="B96" s="52"/>
-      <c r="C96" s="52"/>
-      <c r="D96" s="52"/>
-      <c r="E96" s="52"/>
-      <c r="F96" s="52"/>
-      <c r="G96" s="52"/>
-      <c r="H96" s="52"/>
-      <c r="I96" s="52"/>
-      <c r="J96" s="52"/>
-      <c r="K96" s="52"/>
-      <c r="L96" s="52"/>
-      <c r="M96" s="52"/>
-      <c r="N96" s="52"/>
-      <c r="O96" s="52"/>
-      <c r="P96" s="52"/>
-      <c r="Q96" s="52"/>
-      <c r="R96" s="52"/>
-      <c r="S96" s="52"/>
-      <c r="T96" s="52"/>
-      <c r="U96" s="52"/>
-      <c r="V96" s="52"/>
-      <c r="W96" s="52"/>
-      <c r="X96" s="52"/>
-    </row>
-    <row r="97" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A97" s="52"/>
-      <c r="B97" s="52"/>
-      <c r="C97" s="52"/>
-      <c r="D97" s="52"/>
-      <c r="E97" s="52"/>
-      <c r="F97" s="52"/>
-      <c r="G97" s="52"/>
-      <c r="H97" s="52"/>
-      <c r="I97" s="52"/>
-      <c r="J97" s="52"/>
-      <c r="K97" s="52"/>
-      <c r="L97" s="52"/>
-      <c r="M97" s="52"/>
-      <c r="N97" s="52"/>
-      <c r="O97" s="52"/>
-      <c r="P97" s="52"/>
-      <c r="Q97" s="52"/>
-      <c r="R97" s="52"/>
-      <c r="S97" s="52"/>
-      <c r="T97" s="52"/>
-      <c r="U97" s="52"/>
-      <c r="V97" s="52"/>
-      <c r="W97" s="52"/>
-      <c r="X97" s="52"/>
-    </row>
-    <row r="98" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A98" s="52"/>
-      <c r="B98" s="52"/>
-      <c r="C98" s="52"/>
-      <c r="D98" s="52"/>
-      <c r="E98" s="52"/>
-      <c r="F98" s="52"/>
-      <c r="G98" s="52"/>
-      <c r="H98" s="52"/>
-      <c r="I98" s="52"/>
-      <c r="J98" s="52"/>
-      <c r="K98" s="52"/>
-      <c r="L98" s="52"/>
-      <c r="M98" s="52"/>
-      <c r="N98" s="52"/>
-      <c r="O98" s="52"/>
-      <c r="P98" s="52"/>
-      <c r="Q98" s="52"/>
-      <c r="R98" s="52"/>
-      <c r="S98" s="52"/>
-      <c r="T98" s="52"/>
-      <c r="U98" s="52"/>
-      <c r="V98" s="52"/>
-      <c r="W98" s="52"/>
-      <c r="X98" s="52"/>
-    </row>
-    <row r="99" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A99" s="52"/>
-      <c r="B99" s="52"/>
-      <c r="C99" s="52"/>
-      <c r="D99" s="52"/>
-      <c r="E99" s="52"/>
-      <c r="F99" s="52"/>
-      <c r="G99" s="52"/>
-      <c r="H99" s="52"/>
-      <c r="I99" s="52"/>
-      <c r="J99" s="52"/>
-      <c r="K99" s="52"/>
-      <c r="L99" s="52"/>
-      <c r="M99" s="52"/>
-      <c r="N99" s="52"/>
-      <c r="O99" s="52"/>
-      <c r="P99" s="52"/>
-      <c r="Q99" s="52"/>
-      <c r="R99" s="52"/>
-      <c r="S99" s="52"/>
-      <c r="T99" s="52"/>
-      <c r="U99" s="52"/>
-      <c r="V99" s="52"/>
-      <c r="W99" s="52"/>
-      <c r="X99" s="52"/>
-    </row>
-    <row r="100" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A100" s="52"/>
-      <c r="B100" s="52"/>
-      <c r="C100" s="52"/>
-      <c r="D100" s="52"/>
-      <c r="E100" s="52"/>
-      <c r="F100" s="52"/>
-      <c r="G100" s="52"/>
-      <c r="H100" s="52"/>
-      <c r="I100" s="52"/>
-      <c r="J100" s="52"/>
-      <c r="K100" s="52"/>
-      <c r="L100" s="52"/>
-      <c r="M100" s="52"/>
-      <c r="N100" s="52"/>
-      <c r="O100" s="52"/>
-      <c r="P100" s="52"/>
-      <c r="Q100" s="52"/>
-      <c r="R100" s="52"/>
-      <c r="S100" s="52"/>
-      <c r="T100" s="52"/>
-      <c r="U100" s="52"/>
-      <c r="V100" s="52"/>
-      <c r="W100" s="52"/>
-      <c r="X100" s="52"/>
-    </row>
-    <row r="101" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A101" s="52"/>
-      <c r="B101" s="52"/>
-      <c r="C101" s="52"/>
-      <c r="D101" s="52"/>
-      <c r="E101" s="52"/>
-      <c r="F101" s="52"/>
-      <c r="G101" s="52"/>
-      <c r="H101" s="52"/>
-      <c r="I101" s="52"/>
-      <c r="J101" s="52"/>
-      <c r="K101" s="52"/>
-      <c r="L101" s="52"/>
-      <c r="M101" s="52"/>
-      <c r="N101" s="52"/>
-      <c r="O101" s="52"/>
-      <c r="P101" s="52"/>
-      <c r="Q101" s="52"/>
-      <c r="R101" s="52"/>
-      <c r="S101" s="52"/>
-      <c r="T101" s="52"/>
-      <c r="U101" s="52"/>
-      <c r="V101" s="52"/>
-      <c r="W101" s="52"/>
-      <c r="X101" s="52"/>
-    </row>
-    <row r="102" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A102" s="52"/>
-      <c r="B102" s="52"/>
-      <c r="C102" s="52"/>
-      <c r="D102" s="52"/>
-      <c r="E102" s="52"/>
-      <c r="F102" s="52"/>
-      <c r="G102" s="52"/>
-      <c r="H102" s="52"/>
-      <c r="I102" s="52"/>
-      <c r="J102" s="52"/>
-      <c r="K102" s="52"/>
-      <c r="L102" s="52"/>
-      <c r="M102" s="52"/>
-      <c r="N102" s="52"/>
-      <c r="O102" s="52"/>
-      <c r="P102" s="52"/>
-      <c r="Q102" s="52"/>
-      <c r="R102" s="52"/>
-      <c r="S102" s="52"/>
-      <c r="T102" s="52"/>
-      <c r="U102" s="52"/>
-      <c r="V102" s="52"/>
-      <c r="W102" s="52"/>
-      <c r="X102" s="52"/>
-    </row>
-    <row r="103" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A103" s="52"/>
-      <c r="B103" s="52"/>
-      <c r="C103" s="52"/>
-      <c r="D103" s="52"/>
-      <c r="E103" s="52"/>
-      <c r="F103" s="52"/>
-      <c r="G103" s="52"/>
-      <c r="H103" s="52"/>
-      <c r="I103" s="52"/>
-      <c r="J103" s="52"/>
-      <c r="K103" s="52"/>
-      <c r="L103" s="52"/>
-      <c r="M103" s="52"/>
-      <c r="N103" s="52"/>
-      <c r="O103" s="52"/>
-      <c r="P103" s="52"/>
-      <c r="Q103" s="52"/>
-      <c r="R103" s="52"/>
-      <c r="S103" s="52"/>
-      <c r="T103" s="52"/>
-      <c r="U103" s="52"/>
-      <c r="V103" s="52"/>
-      <c r="W103" s="52"/>
-      <c r="X103" s="52"/>
-    </row>
-    <row r="104" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A104" s="52"/>
-      <c r="B104" s="52"/>
-      <c r="C104" s="52"/>
-      <c r="D104" s="52"/>
-      <c r="E104" s="52"/>
-      <c r="F104" s="52"/>
-      <c r="G104" s="52"/>
-      <c r="H104" s="52"/>
-      <c r="I104" s="52"/>
-      <c r="J104" s="52"/>
-      <c r="K104" s="52"/>
-      <c r="L104" s="52"/>
-      <c r="M104" s="52"/>
-      <c r="N104" s="52"/>
-      <c r="O104" s="52"/>
-      <c r="P104" s="52"/>
-      <c r="Q104" s="52"/>
-      <c r="R104" s="52"/>
-      <c r="S104" s="52"/>
-      <c r="T104" s="52"/>
-      <c r="U104" s="52"/>
-      <c r="V104" s="52"/>
-      <c r="W104" s="52"/>
-      <c r="X104" s="52"/>
-    </row>
-    <row r="105" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A105" s="52"/>
-      <c r="B105" s="52"/>
-      <c r="C105" s="52"/>
-      <c r="D105" s="52"/>
-      <c r="E105" s="52"/>
-      <c r="F105" s="52"/>
-      <c r="G105" s="52"/>
-      <c r="H105" s="52"/>
-      <c r="I105" s="52"/>
-      <c r="J105" s="52"/>
-      <c r="K105" s="52"/>
-      <c r="L105" s="52"/>
-      <c r="M105" s="52"/>
-      <c r="N105" s="52"/>
-      <c r="O105" s="52"/>
-      <c r="P105" s="52"/>
-      <c r="Q105" s="52"/>
-      <c r="R105" s="52"/>
-      <c r="S105" s="52"/>
-      <c r="T105" s="52"/>
-      <c r="U105" s="52"/>
-      <c r="V105" s="52"/>
-      <c r="W105" s="52"/>
-      <c r="X105" s="52"/>
-    </row>
-    <row r="106" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A106" s="52"/>
-      <c r="B106" s="52"/>
-      <c r="C106" s="52"/>
-      <c r="D106" s="52"/>
-      <c r="E106" s="52"/>
-      <c r="F106" s="52"/>
-      <c r="G106" s="52"/>
-      <c r="H106" s="52"/>
-      <c r="I106" s="52"/>
-      <c r="J106" s="52"/>
-      <c r="K106" s="52"/>
-      <c r="L106" s="52"/>
-      <c r="M106" s="52"/>
-      <c r="N106" s="52"/>
-      <c r="O106" s="52"/>
-      <c r="P106" s="52"/>
-      <c r="Q106" s="52"/>
-      <c r="R106" s="52"/>
-      <c r="S106" s="52"/>
-      <c r="T106" s="52"/>
-      <c r="U106" s="52"/>
-      <c r="V106" s="52"/>
-      <c r="W106" s="52"/>
-      <c r="X106" s="52"/>
-    </row>
-    <row r="107" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A107" s="52"/>
-      <c r="B107" s="52"/>
-      <c r="C107" s="52"/>
-      <c r="D107" s="52"/>
-      <c r="E107" s="52"/>
-      <c r="F107" s="52"/>
-      <c r="G107" s="52"/>
-      <c r="H107" s="52"/>
-      <c r="I107" s="52"/>
-      <c r="J107" s="52"/>
-      <c r="K107" s="52"/>
-      <c r="L107" s="52"/>
-      <c r="M107" s="52"/>
-      <c r="N107" s="52"/>
-      <c r="O107" s="52"/>
-      <c r="P107" s="52"/>
-      <c r="Q107" s="52"/>
-      <c r="R107" s="52"/>
-      <c r="S107" s="52"/>
-      <c r="T107" s="52"/>
-      <c r="U107" s="52"/>
-      <c r="V107" s="52"/>
-      <c r="W107" s="52"/>
-      <c r="X107" s="52"/>
-    </row>
-    <row r="108" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A108" s="52"/>
-      <c r="B108" s="52"/>
-      <c r="C108" s="52"/>
-      <c r="D108" s="52"/>
-      <c r="E108" s="52"/>
-      <c r="F108" s="52"/>
-      <c r="G108" s="52"/>
-      <c r="H108" s="52"/>
-      <c r="I108" s="52"/>
-      <c r="J108" s="52"/>
-      <c r="K108" s="52"/>
-      <c r="L108" s="52"/>
-      <c r="M108" s="52"/>
-      <c r="N108" s="52"/>
-      <c r="O108" s="52"/>
-      <c r="P108" s="52"/>
-      <c r="Q108" s="52"/>
-      <c r="R108" s="52"/>
-      <c r="S108" s="52"/>
-      <c r="T108" s="52"/>
-      <c r="U108" s="52"/>
-      <c r="V108" s="52"/>
-      <c r="W108" s="52"/>
-      <c r="X108" s="52"/>
-    </row>
-    <row r="109" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A109" s="52"/>
-      <c r="B109" s="52"/>
-      <c r="C109" s="52"/>
-      <c r="D109" s="52"/>
-      <c r="E109" s="52"/>
-      <c r="F109" s="52"/>
-      <c r="G109" s="52"/>
-      <c r="H109" s="52"/>
-      <c r="I109" s="52"/>
-      <c r="J109" s="52"/>
-      <c r="K109" s="52"/>
-      <c r="L109" s="52"/>
-      <c r="M109" s="52"/>
-      <c r="N109" s="52"/>
-      <c r="O109" s="52"/>
-      <c r="P109" s="52"/>
-      <c r="Q109" s="52"/>
-      <c r="R109" s="52"/>
-      <c r="S109" s="52"/>
-      <c r="T109" s="52"/>
-      <c r="U109" s="52"/>
-      <c r="V109" s="52"/>
-      <c r="W109" s="52"/>
-      <c r="X109" s="52"/>
-    </row>
-    <row r="110" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A110" s="52"/>
-      <c r="B110" s="52"/>
-      <c r="C110" s="52"/>
-      <c r="D110" s="52"/>
-      <c r="E110" s="52"/>
-      <c r="F110" s="52"/>
-      <c r="G110" s="52"/>
-      <c r="H110" s="52"/>
-      <c r="I110" s="52"/>
-      <c r="J110" s="52"/>
-      <c r="K110" s="52"/>
-      <c r="L110" s="52"/>
-      <c r="M110" s="52"/>
-      <c r="N110" s="52"/>
-      <c r="O110" s="52"/>
-      <c r="P110" s="52"/>
-      <c r="Q110" s="52"/>
-      <c r="R110" s="52"/>
-      <c r="S110" s="52"/>
-      <c r="T110" s="52"/>
-      <c r="U110" s="52"/>
-      <c r="V110" s="52"/>
-      <c r="W110" s="52"/>
-      <c r="X110" s="52"/>
-    </row>
-    <row r="111" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A111" s="52"/>
-      <c r="B111" s="52"/>
-      <c r="C111" s="52"/>
-      <c r="D111" s="52"/>
-      <c r="E111" s="52"/>
-      <c r="F111" s="52"/>
-      <c r="G111" s="52"/>
-      <c r="H111" s="52"/>
-      <c r="I111" s="52"/>
-      <c r="J111" s="52"/>
-      <c r="K111" s="52"/>
-      <c r="L111" s="52"/>
-      <c r="M111" s="52"/>
-      <c r="N111" s="52"/>
-      <c r="O111" s="52"/>
-      <c r="P111" s="52"/>
-      <c r="Q111" s="52"/>
-      <c r="R111" s="52"/>
-      <c r="S111" s="52"/>
-      <c r="T111" s="52"/>
-      <c r="U111" s="52"/>
-      <c r="V111" s="52"/>
-      <c r="W111" s="52"/>
-      <c r="X111" s="52"/>
-    </row>
-    <row r="112" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A112" s="52"/>
-      <c r="B112" s="52"/>
-      <c r="C112" s="52"/>
-      <c r="D112" s="52"/>
-      <c r="E112" s="52"/>
-      <c r="F112" s="52"/>
-      <c r="G112" s="52"/>
-      <c r="H112" s="52"/>
-      <c r="I112" s="52"/>
-      <c r="J112" s="52"/>
-      <c r="K112" s="52"/>
-      <c r="L112" s="52"/>
-      <c r="M112" s="52"/>
-      <c r="N112" s="52"/>
-      <c r="O112" s="52"/>
-      <c r="P112" s="52"/>
-      <c r="Q112" s="52"/>
-      <c r="R112" s="52"/>
-      <c r="S112" s="52"/>
-      <c r="T112" s="52"/>
-      <c r="U112" s="52"/>
-      <c r="V112" s="52"/>
-      <c r="W112" s="52"/>
-      <c r="X112" s="52"/>
-    </row>
-    <row r="113" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A113" s="52"/>
-      <c r="B113" s="52"/>
-      <c r="C113" s="52"/>
-      <c r="D113" s="52"/>
-      <c r="E113" s="52"/>
-      <c r="F113" s="52"/>
-      <c r="G113" s="52"/>
-      <c r="H113" s="52"/>
-      <c r="I113" s="52"/>
-      <c r="J113" s="52"/>
-      <c r="K113" s="52"/>
-      <c r="L113" s="52"/>
-      <c r="M113" s="52"/>
-      <c r="N113" s="52"/>
-      <c r="O113" s="52"/>
-      <c r="P113" s="52"/>
-      <c r="Q113" s="52"/>
-      <c r="R113" s="52"/>
-      <c r="S113" s="52"/>
-      <c r="T113" s="52"/>
-      <c r="U113" s="52"/>
-      <c r="V113" s="52"/>
-      <c r="W113" s="52"/>
-      <c r="X113" s="52"/>
-    </row>
-    <row r="114" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A114" s="52"/>
-      <c r="B114" s="52"/>
-      <c r="C114" s="52"/>
-      <c r="D114" s="52"/>
-      <c r="E114" s="52"/>
-      <c r="F114" s="52"/>
-      <c r="G114" s="52"/>
-      <c r="H114" s="52"/>
-      <c r="I114" s="52"/>
-      <c r="J114" s="52"/>
-      <c r="K114" s="52"/>
-      <c r="L114" s="52"/>
-      <c r="M114" s="52"/>
-      <c r="N114" s="52"/>
-      <c r="O114" s="52"/>
-      <c r="P114" s="52"/>
-      <c r="Q114" s="52"/>
-      <c r="R114" s="52"/>
-      <c r="S114" s="52"/>
-      <c r="T114" s="52"/>
-      <c r="U114" s="52"/>
-      <c r="V114" s="52"/>
-      <c r="W114" s="52"/>
-      <c r="X114" s="52"/>
-    </row>
-    <row r="115" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A115" s="52"/>
-      <c r="B115" s="52"/>
-      <c r="C115" s="52"/>
-      <c r="D115" s="52"/>
-      <c r="E115" s="52"/>
-      <c r="F115" s="52"/>
-      <c r="G115" s="52"/>
-      <c r="H115" s="52"/>
-      <c r="I115" s="52"/>
-      <c r="J115" s="52"/>
-      <c r="K115" s="52"/>
-      <c r="L115" s="52"/>
-      <c r="M115" s="52"/>
-      <c r="N115" s="52"/>
-      <c r="O115" s="52"/>
-      <c r="P115" s="52"/>
-      <c r="Q115" s="52"/>
-      <c r="R115" s="52"/>
-      <c r="S115" s="52"/>
-      <c r="T115" s="52"/>
-      <c r="U115" s="52"/>
-      <c r="V115" s="52"/>
-      <c r="W115" s="52"/>
-      <c r="X115" s="52"/>
-    </row>
-    <row r="116" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A116" s="52"/>
-      <c r="B116" s="52"/>
-      <c r="C116" s="52"/>
-      <c r="D116" s="52"/>
-      <c r="E116" s="52"/>
-      <c r="F116" s="52"/>
-      <c r="G116" s="52"/>
-      <c r="H116" s="52"/>
-      <c r="I116" s="52"/>
-      <c r="J116" s="52"/>
-      <c r="K116" s="52"/>
-      <c r="L116" s="52"/>
-      <c r="M116" s="52"/>
-      <c r="N116" s="52"/>
-      <c r="O116" s="52"/>
-      <c r="P116" s="52"/>
-      <c r="Q116" s="52"/>
-      <c r="R116" s="52"/>
-      <c r="S116" s="52"/>
-      <c r="T116" s="52"/>
-      <c r="U116" s="52"/>
-      <c r="V116" s="52"/>
-      <c r="W116" s="52"/>
-      <c r="X116" s="52"/>
-    </row>
-    <row r="117" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A117" s="52"/>
-      <c r="B117" s="52"/>
-      <c r="C117" s="52"/>
-      <c r="D117" s="52"/>
-      <c r="E117" s="52"/>
-      <c r="F117" s="52"/>
-      <c r="G117" s="52"/>
-      <c r="H117" s="52"/>
-      <c r="I117" s="52"/>
-      <c r="J117" s="52"/>
-      <c r="K117" s="52"/>
-      <c r="L117" s="52"/>
-      <c r="M117" s="52"/>
-      <c r="N117" s="52"/>
-      <c r="O117" s="52"/>
-      <c r="P117" s="52"/>
-      <c r="Q117" s="52"/>
-      <c r="R117" s="52"/>
-      <c r="S117" s="52"/>
-      <c r="T117" s="52"/>
-      <c r="U117" s="52"/>
-      <c r="V117" s="52"/>
-      <c r="W117" s="52"/>
-      <c r="X117" s="52"/>
-    </row>
-    <row r="118" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A118" s="52"/>
-      <c r="B118" s="52"/>
-      <c r="C118" s="52"/>
-      <c r="D118" s="52"/>
-      <c r="E118" s="52"/>
-      <c r="F118" s="52"/>
-      <c r="G118" s="52"/>
-      <c r="H118" s="52"/>
-      <c r="I118" s="52"/>
-      <c r="J118" s="52"/>
-      <c r="K118" s="52"/>
-      <c r="L118" s="52"/>
-      <c r="M118" s="52"/>
-      <c r="N118" s="52"/>
-      <c r="O118" s="52"/>
-      <c r="P118" s="52"/>
-      <c r="Q118" s="52"/>
-      <c r="R118" s="52"/>
-      <c r="S118" s="52"/>
-      <c r="T118" s="52"/>
-      <c r="U118" s="52"/>
-      <c r="V118" s="52"/>
-      <c r="W118" s="52"/>
-      <c r="X118" s="52"/>
-    </row>
-    <row r="119" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A119" s="52"/>
-      <c r="B119" s="52"/>
-      <c r="C119" s="52"/>
-      <c r="D119" s="52"/>
-      <c r="E119" s="52"/>
-      <c r="F119" s="52"/>
-      <c r="G119" s="52"/>
-      <c r="H119" s="52"/>
-      <c r="I119" s="52"/>
-      <c r="J119" s="52"/>
-      <c r="K119" s="52"/>
-      <c r="L119" s="52"/>
-      <c r="M119" s="52"/>
-      <c r="N119" s="52"/>
-      <c r="O119" s="52"/>
-      <c r="P119" s="52"/>
-      <c r="Q119" s="52"/>
-      <c r="R119" s="52"/>
-      <c r="S119" s="52"/>
-      <c r="T119" s="52"/>
-      <c r="U119" s="52"/>
-      <c r="V119" s="52"/>
-      <c r="W119" s="52"/>
-      <c r="X119" s="52"/>
-    </row>
-    <row r="120" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A120" s="52"/>
-      <c r="B120" s="52"/>
-      <c r="C120" s="52"/>
-      <c r="D120" s="52"/>
-      <c r="E120" s="52"/>
-      <c r="F120" s="52"/>
-      <c r="G120" s="52"/>
-      <c r="H120" s="52"/>
-      <c r="I120" s="52"/>
-      <c r="J120" s="52"/>
-      <c r="K120" s="52"/>
-      <c r="L120" s="52"/>
-      <c r="M120" s="52"/>
-      <c r="N120" s="52"/>
-      <c r="O120" s="52"/>
-      <c r="P120" s="52"/>
-      <c r="Q120" s="52"/>
-      <c r="R120" s="52"/>
-      <c r="S120" s="52"/>
-      <c r="T120" s="52"/>
-      <c r="U120" s="52"/>
-      <c r="V120" s="52"/>
-      <c r="W120" s="52"/>
-      <c r="X120" s="52"/>
-    </row>
-    <row r="121" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A121" s="52"/>
-      <c r="B121" s="52"/>
-      <c r="C121" s="52"/>
-      <c r="D121" s="52"/>
-      <c r="E121" s="52"/>
-      <c r="F121" s="52"/>
-      <c r="G121" s="52"/>
-      <c r="H121" s="52"/>
-      <c r="I121" s="52"/>
-      <c r="J121" s="52"/>
-      <c r="K121" s="52"/>
-      <c r="L121" s="52"/>
-      <c r="M121" s="52"/>
-      <c r="N121" s="52"/>
-      <c r="O121" s="52"/>
-      <c r="P121" s="52"/>
-      <c r="Q121" s="52"/>
-      <c r="R121" s="52"/>
-      <c r="S121" s="52"/>
-      <c r="T121" s="52"/>
-      <c r="U121" s="52"/>
-      <c r="V121" s="52"/>
-      <c r="W121" s="52"/>
-      <c r="X121" s="52"/>
-    </row>
-    <row r="122" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A122" s="52"/>
-      <c r="B122" s="52"/>
-      <c r="C122" s="52"/>
-      <c r="D122" s="52"/>
-      <c r="E122" s="52"/>
-      <c r="F122" s="52"/>
-      <c r="G122" s="52"/>
-      <c r="H122" s="52"/>
-      <c r="I122" s="52"/>
-      <c r="J122" s="52"/>
-      <c r="K122" s="52"/>
-      <c r="L122" s="52"/>
-      <c r="M122" s="52"/>
-      <c r="N122" s="52"/>
-      <c r="O122" s="52"/>
-      <c r="P122" s="52"/>
-      <c r="Q122" s="52"/>
-      <c r="R122" s="52"/>
-      <c r="S122" s="52"/>
-      <c r="T122" s="52"/>
-      <c r="U122" s="52"/>
-      <c r="V122" s="52"/>
-      <c r="W122" s="52"/>
-      <c r="X122" s="52"/>
-    </row>
-    <row r="123" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A123" s="52"/>
-      <c r="B123" s="52"/>
-      <c r="C123" s="52"/>
-      <c r="D123" s="52"/>
-      <c r="E123" s="52"/>
-      <c r="F123" s="52"/>
-      <c r="G123" s="52"/>
-      <c r="H123" s="52"/>
-      <c r="I123" s="52"/>
-      <c r="J123" s="52"/>
-      <c r="K123" s="52"/>
-      <c r="L123" s="52"/>
-      <c r="M123" s="52"/>
-      <c r="N123" s="52"/>
-      <c r="O123" s="52"/>
-      <c r="P123" s="52"/>
-      <c r="Q123" s="52"/>
-      <c r="R123" s="52"/>
-      <c r="S123" s="52"/>
-      <c r="T123" s="52"/>
-      <c r="U123" s="52"/>
-      <c r="V123" s="52"/>
-      <c r="W123" s="52"/>
-      <c r="X123" s="52"/>
-    </row>
-    <row r="124" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A124" s="52"/>
-      <c r="B124" s="52"/>
-      <c r="C124" s="52"/>
-      <c r="D124" s="52"/>
-      <c r="E124" s="52"/>
-      <c r="F124" s="52"/>
-      <c r="G124" s="52"/>
-      <c r="H124" s="52"/>
-      <c r="I124" s="52"/>
-      <c r="J124" s="52"/>
-      <c r="K124" s="52"/>
-      <c r="L124" s="52"/>
-      <c r="M124" s="52"/>
-      <c r="N124" s="52"/>
-      <c r="O124" s="52"/>
-      <c r="P124" s="52"/>
-      <c r="Q124" s="52"/>
-      <c r="R124" s="52"/>
-      <c r="S124" s="52"/>
-      <c r="T124" s="52"/>
-      <c r="U124" s="52"/>
-      <c r="V124" s="52"/>
-      <c r="W124" s="52"/>
-      <c r="X124" s="52"/>
-    </row>
-    <row r="125" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A125" s="52"/>
-      <c r="B125" s="52"/>
-      <c r="C125" s="52"/>
-      <c r="D125" s="52"/>
-      <c r="E125" s="52"/>
-      <c r="F125" s="52"/>
-      <c r="G125" s="52"/>
-      <c r="H125" s="52"/>
-      <c r="I125" s="52"/>
-      <c r="J125" s="52"/>
-      <c r="K125" s="52"/>
-      <c r="L125" s="52"/>
-      <c r="M125" s="52"/>
-      <c r="N125" s="52"/>
-      <c r="O125" s="52"/>
-      <c r="P125" s="52"/>
-      <c r="Q125" s="52"/>
-      <c r="R125" s="52"/>
-      <c r="S125" s="52"/>
-      <c r="T125" s="52"/>
-      <c r="U125" s="52"/>
-      <c r="V125" s="52"/>
-      <c r="W125" s="52"/>
-      <c r="X125" s="52"/>
-    </row>
-    <row r="126" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A126" s="52"/>
-      <c r="B126" s="52"/>
-      <c r="C126" s="52"/>
-      <c r="D126" s="52"/>
-      <c r="E126" s="52"/>
-      <c r="F126" s="52"/>
-      <c r="G126" s="52"/>
-      <c r="H126" s="52"/>
-      <c r="I126" s="52"/>
-      <c r="J126" s="52"/>
-      <c r="K126" s="52"/>
-      <c r="L126" s="52"/>
-      <c r="M126" s="52"/>
-      <c r="N126" s="52"/>
-      <c r="O126" s="52"/>
-      <c r="P126" s="52"/>
-      <c r="Q126" s="52"/>
-      <c r="R126" s="52"/>
-      <c r="S126" s="52"/>
-      <c r="T126" s="52"/>
-      <c r="U126" s="52"/>
-      <c r="V126" s="52"/>
-      <c r="W126" s="52"/>
-      <c r="X126" s="52"/>
-    </row>
-    <row r="127" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A127" s="52"/>
-      <c r="B127" s="52"/>
-      <c r="C127" s="52"/>
-      <c r="D127" s="52"/>
-      <c r="E127" s="52"/>
-      <c r="F127" s="52"/>
-      <c r="G127" s="52"/>
-      <c r="H127" s="52"/>
-      <c r="I127" s="52"/>
-      <c r="J127" s="52"/>
-      <c r="K127" s="52"/>
-      <c r="L127" s="52"/>
-      <c r="M127" s="52"/>
-      <c r="N127" s="52"/>
-      <c r="O127" s="52"/>
-      <c r="P127" s="52"/>
-      <c r="Q127" s="52"/>
-      <c r="R127" s="52"/>
-      <c r="S127" s="52"/>
-      <c r="T127" s="52"/>
-      <c r="U127" s="52"/>
-      <c r="V127" s="52"/>
-      <c r="W127" s="52"/>
-      <c r="X127" s="52"/>
-    </row>
-    <row r="128" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A128" s="52"/>
-      <c r="B128" s="52"/>
-      <c r="C128" s="52"/>
-      <c r="D128" s="52"/>
-      <c r="E128" s="52"/>
-      <c r="F128" s="52"/>
-      <c r="G128" s="52"/>
-      <c r="H128" s="52"/>
-      <c r="I128" s="52"/>
-      <c r="J128" s="52"/>
-      <c r="K128" s="52"/>
-      <c r="L128" s="52"/>
-      <c r="M128" s="52"/>
-      <c r="N128" s="52"/>
-      <c r="O128" s="52"/>
-      <c r="P128" s="52"/>
-      <c r="Q128" s="52"/>
-      <c r="R128" s="52"/>
-      <c r="S128" s="52"/>
-      <c r="T128" s="52"/>
-      <c r="U128" s="52"/>
-      <c r="V128" s="52"/>
-      <c r="W128" s="52"/>
-      <c r="X128" s="52"/>
-    </row>
-    <row r="129" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A129" s="52"/>
-      <c r="B129" s="52"/>
-      <c r="C129" s="52"/>
-      <c r="D129" s="52"/>
-      <c r="E129" s="52"/>
-      <c r="F129" s="52"/>
-      <c r="G129" s="52"/>
-      <c r="H129" s="52"/>
-      <c r="I129" s="52"/>
-      <c r="J129" s="52"/>
-      <c r="K129" s="52"/>
-      <c r="L129" s="52"/>
-      <c r="M129" s="52"/>
-      <c r="N129" s="52"/>
-      <c r="O129" s="52"/>
-      <c r="P129" s="52"/>
-      <c r="Q129" s="52"/>
-      <c r="R129" s="52"/>
-      <c r="S129" s="52"/>
-      <c r="T129" s="52"/>
-      <c r="U129" s="52"/>
-      <c r="V129" s="52"/>
-      <c r="W129" s="52"/>
-      <c r="X129" s="52"/>
-    </row>
-    <row r="130" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A130" s="52"/>
-      <c r="B130" s="52"/>
-      <c r="C130" s="52"/>
-      <c r="D130" s="52"/>
-      <c r="E130" s="52"/>
-      <c r="F130" s="52"/>
-      <c r="G130" s="52"/>
-      <c r="H130" s="52"/>
-      <c r="I130" s="52"/>
-      <c r="J130" s="52"/>
-      <c r="K130" s="52"/>
-      <c r="L130" s="52"/>
-      <c r="M130" s="52"/>
-      <c r="N130" s="52"/>
-      <c r="O130" s="52"/>
-      <c r="P130" s="52"/>
-      <c r="Q130" s="52"/>
-      <c r="R130" s="52"/>
-      <c r="S130" s="52"/>
-      <c r="T130" s="52"/>
-      <c r="U130" s="52"/>
-      <c r="V130" s="52"/>
-      <c r="W130" s="52"/>
-      <c r="X130" s="52"/>
-    </row>
-    <row r="131" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A131" s="52"/>
-      <c r="B131" s="52"/>
-      <c r="C131" s="52"/>
-      <c r="D131" s="52"/>
-      <c r="E131" s="52"/>
-      <c r="F131" s="52"/>
-      <c r="G131" s="52"/>
-      <c r="H131" s="52"/>
-      <c r="I131" s="52"/>
-      <c r="J131" s="52"/>
-      <c r="K131" s="52"/>
-      <c r="L131" s="52"/>
-      <c r="M131" s="52"/>
-      <c r="N131" s="52"/>
-      <c r="O131" s="52"/>
-      <c r="P131" s="52"/>
-      <c r="Q131" s="52"/>
-      <c r="R131" s="52"/>
-      <c r="S131" s="52"/>
-      <c r="T131" s="52"/>
-      <c r="U131" s="52"/>
-      <c r="V131" s="52"/>
-      <c r="W131" s="52"/>
-      <c r="X131" s="52"/>
-    </row>
-    <row r="132" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A132" s="52"/>
-      <c r="B132" s="52"/>
-      <c r="C132" s="52"/>
-      <c r="D132" s="52"/>
-      <c r="E132" s="52"/>
-      <c r="F132" s="52"/>
-      <c r="G132" s="52"/>
-      <c r="H132" s="52"/>
-      <c r="I132" s="52"/>
-      <c r="J132" s="52"/>
-      <c r="K132" s="52"/>
-      <c r="L132" s="52"/>
-      <c r="M132" s="52"/>
-      <c r="N132" s="52"/>
-      <c r="O132" s="52"/>
-      <c r="P132" s="52"/>
-      <c r="Q132" s="52"/>
-      <c r="R132" s="52"/>
-      <c r="S132" s="52"/>
-      <c r="T132" s="52"/>
-      <c r="U132" s="52"/>
-      <c r="V132" s="52"/>
-      <c r="W132" s="52"/>
-      <c r="X132" s="52"/>
-    </row>
-    <row r="133" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A133" s="52"/>
-      <c r="B133" s="52"/>
-      <c r="C133" s="52"/>
-      <c r="D133" s="52"/>
-      <c r="E133" s="52"/>
-      <c r="F133" s="52"/>
-      <c r="G133" s="52"/>
-      <c r="H133" s="52"/>
-      <c r="I133" s="52"/>
-      <c r="J133" s="52"/>
-      <c r="K133" s="52"/>
-      <c r="L133" s="52"/>
-      <c r="M133" s="52"/>
-      <c r="N133" s="52"/>
-      <c r="O133" s="52"/>
-      <c r="P133" s="52"/>
-      <c r="Q133" s="52"/>
-      <c r="R133" s="52"/>
-      <c r="S133" s="52"/>
-      <c r="T133" s="52"/>
-      <c r="U133" s="52"/>
-      <c r="V133" s="52"/>
-      <c r="W133" s="52"/>
-      <c r="X133" s="52"/>
-    </row>
-    <row r="134" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A134" s="52"/>
-      <c r="B134" s="52"/>
-      <c r="C134" s="52"/>
-      <c r="D134" s="52"/>
-      <c r="E134" s="52"/>
-      <c r="F134" s="52"/>
-      <c r="G134" s="52"/>
-      <c r="H134" s="52"/>
-      <c r="I134" s="52"/>
-      <c r="J134" s="52"/>
-      <c r="K134" s="52"/>
-      <c r="L134" s="52"/>
-      <c r="M134" s="52"/>
-      <c r="N134" s="52"/>
-      <c r="O134" s="52"/>
-      <c r="P134" s="52"/>
-      <c r="Q134" s="52"/>
-      <c r="R134" s="52"/>
-      <c r="S134" s="52"/>
-      <c r="T134" s="52"/>
-      <c r="U134" s="52"/>
-      <c r="V134" s="52"/>
-      <c r="W134" s="52"/>
-      <c r="X134" s="52"/>
-    </row>
-    <row r="135" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A135" s="52"/>
-      <c r="B135" s="52"/>
-      <c r="C135" s="52"/>
-      <c r="D135" s="52"/>
-      <c r="E135" s="52"/>
-      <c r="F135" s="52"/>
-      <c r="G135" s="52"/>
-      <c r="H135" s="52"/>
-      <c r="I135" s="52"/>
-      <c r="J135" s="52"/>
-      <c r="K135" s="52"/>
-      <c r="L135" s="52"/>
-      <c r="M135" s="52"/>
-      <c r="N135" s="52"/>
-      <c r="O135" s="52"/>
-      <c r="P135" s="52"/>
-      <c r="Q135" s="52"/>
-      <c r="R135" s="52"/>
-      <c r="S135" s="52"/>
-      <c r="T135" s="52"/>
-      <c r="U135" s="52"/>
-      <c r="V135" s="52"/>
-      <c r="W135" s="52"/>
-      <c r="X135" s="52"/>
-    </row>
-    <row r="136" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A136" s="52"/>
-      <c r="B136" s="52"/>
-      <c r="C136" s="52"/>
-      <c r="D136" s="52"/>
-      <c r="E136" s="52"/>
-      <c r="F136" s="52"/>
-      <c r="G136" s="52"/>
-      <c r="H136" s="52"/>
-      <c r="I136" s="52"/>
-      <c r="J136" s="52"/>
-      <c r="K136" s="52"/>
-      <c r="L136" s="52"/>
-      <c r="M136" s="52"/>
-      <c r="N136" s="52"/>
-      <c r="O136" s="52"/>
-      <c r="P136" s="52"/>
-      <c r="Q136" s="52"/>
-      <c r="R136" s="52"/>
-      <c r="S136" s="52"/>
-      <c r="T136" s="52"/>
-      <c r="U136" s="52"/>
-      <c r="V136" s="52"/>
-      <c r="W136" s="52"/>
-      <c r="X136" s="52"/>
-    </row>
-    <row r="137" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A137" s="52"/>
-      <c r="B137" s="52"/>
-      <c r="C137" s="52"/>
-      <c r="D137" s="52"/>
-      <c r="E137" s="52"/>
-      <c r="F137" s="52"/>
-      <c r="G137" s="52"/>
-      <c r="H137" s="52"/>
-      <c r="I137" s="52"/>
-      <c r="J137" s="52"/>
-      <c r="K137" s="52"/>
-      <c r="L137" s="52"/>
-      <c r="M137" s="52"/>
-      <c r="N137" s="52"/>
-      <c r="O137" s="52"/>
-      <c r="P137" s="52"/>
-      <c r="Q137" s="52"/>
-      <c r="R137" s="52"/>
-      <c r="S137" s="52"/>
-      <c r="T137" s="52"/>
-      <c r="U137" s="52"/>
-      <c r="V137" s="52"/>
-      <c r="W137" s="52"/>
-      <c r="X137" s="52"/>
-    </row>
-    <row r="138" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A138" s="52"/>
-      <c r="B138" s="52"/>
-      <c r="C138" s="52"/>
-      <c r="D138" s="52"/>
-      <c r="E138" s="52"/>
-      <c r="F138" s="52"/>
-      <c r="G138" s="52"/>
-      <c r="H138" s="52"/>
-      <c r="I138" s="52"/>
-      <c r="J138" s="52"/>
-      <c r="K138" s="52"/>
-      <c r="L138" s="52"/>
-      <c r="M138" s="52"/>
-      <c r="N138" s="52"/>
-      <c r="O138" s="52"/>
-      <c r="P138" s="52"/>
-      <c r="Q138" s="52"/>
-      <c r="R138" s="52"/>
-      <c r="S138" s="52"/>
-      <c r="T138" s="52"/>
-      <c r="U138" s="52"/>
-      <c r="V138" s="52"/>
-      <c r="W138" s="52"/>
-      <c r="X138" s="52"/>
-    </row>
-    <row r="139" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A139" s="52"/>
-      <c r="B139" s="52"/>
-      <c r="C139" s="52"/>
-      <c r="D139" s="52"/>
-      <c r="E139" s="52"/>
-      <c r="F139" s="52"/>
-      <c r="G139" s="52"/>
-      <c r="H139" s="52"/>
-      <c r="I139" s="52"/>
-      <c r="J139" s="52"/>
-      <c r="K139" s="52"/>
-      <c r="L139" s="52"/>
-      <c r="M139" s="52"/>
-      <c r="N139" s="52"/>
-      <c r="O139" s="52"/>
-      <c r="P139" s="52"/>
-      <c r="Q139" s="52"/>
-      <c r="R139" s="52"/>
-      <c r="S139" s="52"/>
-      <c r="T139" s="52"/>
-      <c r="U139" s="52"/>
-      <c r="V139" s="52"/>
-      <c r="W139" s="52"/>
-      <c r="X139" s="52"/>
-    </row>
-    <row r="140" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A140" s="52"/>
-      <c r="B140" s="52"/>
-      <c r="C140" s="52"/>
-      <c r="D140" s="52"/>
-      <c r="E140" s="52"/>
-      <c r="F140" s="52"/>
-      <c r="G140" s="52"/>
-      <c r="H140" s="52"/>
-      <c r="I140" s="52"/>
-      <c r="J140" s="52"/>
-      <c r="K140" s="52"/>
-      <c r="L140" s="52"/>
-      <c r="M140" s="52"/>
-      <c r="N140" s="52"/>
-      <c r="O140" s="52"/>
-      <c r="P140" s="52"/>
-      <c r="Q140" s="52"/>
-      <c r="R140" s="52"/>
-      <c r="S140" s="52"/>
-      <c r="T140" s="52"/>
-      <c r="U140" s="52"/>
-      <c r="V140" s="52"/>
-      <c r="W140" s="52"/>
-      <c r="X140" s="52"/>
-    </row>
   </sheetData>
   <mergeCells count="69">
-    <mergeCell ref="A1:F3"/>
-    <mergeCell ref="G1:S3"/>
-    <mergeCell ref="T1:X1"/>
-    <mergeCell ref="T2:X2"/>
-    <mergeCell ref="T3:X3"/>
-    <mergeCell ref="D7:P7"/>
-    <mergeCell ref="Q7:S7"/>
-    <mergeCell ref="T7:X7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A4:X4"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="F5:N5"/>
-    <mergeCell ref="O5:Q5"/>
-    <mergeCell ref="R5:X5"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="E6:Q6"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="T6:X6"/>
-    <mergeCell ref="D8:X8"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="D10:P10"/>
-    <mergeCell ref="Q10:S10"/>
-    <mergeCell ref="T10:X10"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="F9:Q9"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="T9:X9"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="D11:X11"/>
-    <mergeCell ref="A12:X12"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="H13:O13"/>
-    <mergeCell ref="Q13:W13"/>
+    <mergeCell ref="A46:F48"/>
+    <mergeCell ref="G46:S48"/>
+    <mergeCell ref="T46:X46"/>
+    <mergeCell ref="T47:X47"/>
+    <mergeCell ref="T48:X48"/>
+    <mergeCell ref="A44:K44"/>
+    <mergeCell ref="L44:X44"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="G37:O37"/>
+    <mergeCell ref="Q37:W37"/>
+    <mergeCell ref="A38:X38"/>
+    <mergeCell ref="A43:K43"/>
+    <mergeCell ref="L43:X43"/>
+    <mergeCell ref="A33:X33"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="G35:O35"/>
+    <mergeCell ref="Q35:W35"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="G36:O36"/>
+    <mergeCell ref="Q36:W36"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="H14:O14"/>
     <mergeCell ref="Q14:W14"/>
@@ -5246,26 +3815,39 @@
     <mergeCell ref="F24:Q24"/>
     <mergeCell ref="R24:T24"/>
     <mergeCell ref="V24:W24"/>
-    <mergeCell ref="A33:X33"/>
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="G35:O35"/>
-    <mergeCell ref="Q35:W35"/>
-    <mergeCell ref="A36:E36"/>
-    <mergeCell ref="G36:O36"/>
-    <mergeCell ref="Q36:W36"/>
-    <mergeCell ref="A44:K44"/>
-    <mergeCell ref="L44:X44"/>
-    <mergeCell ref="A37:E37"/>
-    <mergeCell ref="G37:O37"/>
-    <mergeCell ref="Q37:W37"/>
-    <mergeCell ref="A38:X38"/>
-    <mergeCell ref="A43:K43"/>
-    <mergeCell ref="L43:X43"/>
-    <mergeCell ref="A46:F48"/>
-    <mergeCell ref="G46:S48"/>
-    <mergeCell ref="T46:X46"/>
-    <mergeCell ref="T47:X47"/>
-    <mergeCell ref="T48:X48"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D11:X11"/>
+    <mergeCell ref="A12:X12"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="H13:O13"/>
+    <mergeCell ref="Q13:W13"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="D10:P10"/>
+    <mergeCell ref="Q10:S10"/>
+    <mergeCell ref="T10:X10"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="F9:Q9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="T9:X9"/>
+    <mergeCell ref="D7:P7"/>
+    <mergeCell ref="Q7:S7"/>
+    <mergeCell ref="T7:X7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A4:X4"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="F5:N5"/>
+    <mergeCell ref="O5:Q5"/>
+    <mergeCell ref="R5:X5"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="E6:Q6"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="T6:X6"/>
+    <mergeCell ref="D8:X8"/>
+    <mergeCell ref="A1:F3"/>
+    <mergeCell ref="G1:S3"/>
+    <mergeCell ref="T1:X1"/>
+    <mergeCell ref="T2:X2"/>
+    <mergeCell ref="T3:X3"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="95" fitToHeight="0" orientation="portrait" r:id="rId1"/>
